--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_furn_home_furnishings.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_furn_home_furnishings.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="sase_1213" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.07389999999999999</v>
+        <v>-0.0486</v>
       </c>
       <c r="G2">
-        <v>-0.04456633527596846</v>
+        <v>0.01293103448275862</v>
       </c>
       <c r="H2">
-        <v>-0.04456633527596846</v>
+        <v>0.01293103448275862</v>
       </c>
       <c r="I2">
-        <v>-0.1099417209461776</v>
+        <v>-0.09435736677115987</v>
       </c>
       <c r="J2">
-        <v>-0.1099417209461776</v>
+        <v>-0.09435736677115987</v>
       </c>
       <c r="K2">
-        <v>-40.95</v>
+        <v>-36.85</v>
       </c>
       <c r="L2">
-        <v>-0.1403839561193007</v>
+        <v>-0.144396551724138</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +632,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>12.031</v>
+        <v>10.698</v>
       </c>
       <c r="V2">
-        <v>0.02119626497533474</v>
+        <v>0.01633033124713784</v>
       </c>
       <c r="W2">
-        <v>-0.1459412780656304</v>
+        <v>-0.06962025316455696</v>
       </c>
       <c r="X2">
-        <v>0.126632539573072</v>
+        <v>0.09957741353671265</v>
       </c>
       <c r="Y2">
-        <v>-0.2725738176387024</v>
+        <v>-0.1691976667012696</v>
       </c>
       <c r="Z2">
-        <v>0.6275223515846176</v>
+        <v>0.4854304295640827</v>
       </c>
       <c r="AA2">
-        <v>-0.1152319576629252</v>
+        <v>-0.03943277470235838</v>
       </c>
       <c r="AB2">
-        <v>0.1161757210640862</v>
+        <v>0.09083901033990269</v>
       </c>
       <c r="AC2">
-        <v>-0.2317432087301045</v>
+        <v>-0.1296968344006181</v>
       </c>
       <c r="AD2">
-        <v>123.25</v>
+        <v>131.54</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>123.25</v>
+        <v>131.54</v>
       </c>
       <c r="AG2">
-        <v>111.219</v>
+        <v>120.842</v>
       </c>
       <c r="AH2">
-        <v>0.1784034160816386</v>
+        <v>0.1672175327977219</v>
       </c>
       <c r="AI2">
-        <v>0.2214933956330308</v>
+        <v>0.249393295919915</v>
       </c>
       <c r="AJ2">
-        <v>0.1638419077839601</v>
+        <v>0.1557358668560279</v>
       </c>
       <c r="AK2">
-        <v>0.2042893433182897</v>
+        <v>0.233853644565373</v>
       </c>
       <c r="AL2">
-        <v>3.239</v>
+        <v>6.714</v>
       </c>
       <c r="AM2">
-        <v>2.666</v>
+        <v>6.232</v>
       </c>
       <c r="AN2">
-        <v>-10.08509941903281</v>
+        <v>-28.84649122807017</v>
       </c>
       <c r="AO2">
-        <v>-9.901204075331894</v>
+        <v>-3.586535597259457</v>
       </c>
       <c r="AP2">
-        <v>-9.100646428279191</v>
+        <v>-26.50043859649122</v>
       </c>
       <c r="AQ2">
-        <v>-12.02925731432858</v>
+        <v>-3.86392811296534</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +709,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Al Abdullatif Industrial Investment Company (SASE:2340)</t>
+          <t>Naseej International Trading Company (SASE:1213)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,25 +718,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0201</v>
+        <v>-0.09050000000000001</v>
       </c>
       <c r="G3">
-        <v>0.03874930206588498</v>
+        <v>0.1015536723163842</v>
       </c>
       <c r="H3">
-        <v>0.03874930206588498</v>
+        <v>0.1015536723163842</v>
       </c>
       <c r="I3">
-        <v>-0.06588498045784479</v>
+        <v>0.02429378531073446</v>
       </c>
       <c r="J3">
-        <v>-0.06588498045784479</v>
+        <v>0.02429378531073446</v>
       </c>
       <c r="K3">
-        <v>-18.3</v>
+        <v>-1.55</v>
       </c>
       <c r="L3">
-        <v>-0.102177554438861</v>
+        <v>-0.02189265536723164</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +760,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>6.09</v>
+        <v>0.648</v>
       </c>
       <c r="V3">
-        <v>0.01803375777317145</v>
+        <v>0.003760882182240279</v>
       </c>
       <c r="W3">
-        <v>-0.06118355065195587</v>
+        <v>-0.04889589905362776</v>
       </c>
       <c r="X3">
-        <v>0.126632539573072</v>
+        <v>0.1042996443492179</v>
       </c>
       <c r="Y3">
-        <v>-0.1878160902250278</v>
+        <v>-0.1531955434028457</v>
       </c>
       <c r="Z3">
-        <v>0.5429246998908693</v>
+        <v>0.7771764783367544</v>
       </c>
       <c r="AA3">
-        <v>-0.03577058324239117</v>
+        <v>0.01888055851326579</v>
       </c>
       <c r="AB3">
-        <v>0.1161757210640862</v>
+        <v>0.09083901033990269</v>
       </c>
       <c r="AC3">
-        <v>-0.1519463043064774</v>
+        <v>-0.0719584518266369</v>
       </c>
       <c r="AD3">
-        <v>54.1</v>
+        <v>52.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>54.1</v>
+        <v>52.7</v>
       </c>
       <c r="AG3">
-        <v>48.01000000000001</v>
+        <v>52.052</v>
       </c>
       <c r="AH3">
-        <v>0.1380806533945891</v>
+        <v>0.2342222222222222</v>
       </c>
       <c r="AI3">
-        <v>0.1346776201145133</v>
+        <v>0.6403402187120291</v>
       </c>
       <c r="AJ3">
-        <v>0.1244717533898525</v>
+        <v>0.2320104122093853</v>
       </c>
       <c r="AK3">
-        <v>0.121356891888476</v>
+        <v>0.6374859158379464</v>
       </c>
       <c r="AL3">
-        <v>1.3</v>
+        <v>2.49</v>
       </c>
       <c r="AM3">
-        <v>1.252</v>
+        <v>2.49</v>
       </c>
       <c r="AN3">
-        <v>55.26046986721144</v>
+        <v>9.669724770642203</v>
       </c>
       <c r="AO3">
-        <v>-9.076923076923077</v>
+        <v>0.6907630522088353</v>
       </c>
       <c r="AP3">
-        <v>49.03983656792646</v>
+        <v>9.550825688073393</v>
       </c>
       <c r="AQ3">
-        <v>-9.424920127795527</v>
+        <v>0.6907630522088353</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +837,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Naseej International Trading Company (SASE:1213)</t>
+          <t>Al Abdullatif Industrial Investment Company (SASE:2340)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,25 +846,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.12</v>
+        <v>-0.0486</v>
       </c>
       <c r="G4">
-        <v>-0.217948717948718</v>
+        <v>0.02529699510831587</v>
       </c>
       <c r="H4">
-        <v>-0.217948717948718</v>
+        <v>0.02529699510831587</v>
       </c>
       <c r="I4">
-        <v>-0.1538461538461539</v>
+        <v>-0.1090146750524109</v>
       </c>
       <c r="J4">
-        <v>-0.1538461538461539</v>
+        <v>-0.1090146750524109</v>
       </c>
       <c r="K4">
-        <v>-14.2</v>
+        <v>-24.2</v>
       </c>
       <c r="L4">
-        <v>-0.2022792022792023</v>
+        <v>-0.1691125087351502</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -886,73 +888,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.901</v>
+        <v>6.87</v>
       </c>
       <c r="V4">
-        <v>0.007520868113522538</v>
+        <v>0.01900940785832872</v>
       </c>
       <c r="W4">
-        <v>-1.58659217877095</v>
+        <v>-0.06962025316455696</v>
       </c>
       <c r="X4">
-        <v>0.1480044102996347</v>
+        <v>0.09957741353671265</v>
       </c>
       <c r="Y4">
-        <v>-1.734596589070585</v>
+        <v>-0.1691976667012696</v>
       </c>
       <c r="Z4">
-        <v>0.7490077248090137</v>
+        <v>0.3617198756350951</v>
       </c>
       <c r="AA4">
-        <v>-0.1152319576629252</v>
+        <v>-0.03943277470235838</v>
       </c>
       <c r="AB4">
-        <v>0.1165112510671793</v>
+        <v>0.09026405969825972</v>
       </c>
       <c r="AC4">
-        <v>-0.2317432087301045</v>
+        <v>-0.1296968344006181</v>
       </c>
       <c r="AD4">
-        <v>60.3</v>
+        <v>70</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>60.3</v>
+        <v>70</v>
       </c>
       <c r="AG4">
-        <v>59.39899999999999</v>
+        <v>63.13</v>
       </c>
       <c r="AH4">
-        <v>0.3348139922265408</v>
+        <v>0.162262401483542</v>
       </c>
       <c r="AI4">
-        <v>0.6554347826086956</v>
+        <v>0.1773948302078054</v>
       </c>
       <c r="AJ4">
-        <v>0.3314694836466721</v>
+        <v>0.1487056273997126</v>
       </c>
       <c r="AK4">
-        <v>0.6520269157729504</v>
+        <v>0.1628194877878936</v>
       </c>
       <c r="AL4">
-        <v>1.77</v>
+        <v>3.61</v>
       </c>
       <c r="AM4">
-        <v>1.77</v>
+        <v>3.582</v>
       </c>
       <c r="AN4">
-        <v>-9.5260663507109</v>
+        <v>-26.11940298507463</v>
       </c>
       <c r="AO4">
-        <v>-6.101694915254238</v>
+        <v>-4.321329639889197</v>
       </c>
       <c r="AP4">
-        <v>-9.383728278041072</v>
+        <v>-23.55597014925373</v>
       </c>
       <c r="AQ4">
-        <v>-6.101694915254238</v>
+        <v>-4.355108877721944</v>
       </c>
     </row>
     <row r="5">
@@ -972,25 +974,25 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.07389999999999999</v>
+        <v>-0.0461</v>
       </c>
       <c r="G5">
-        <v>-0.1094339622641509</v>
+        <v>-0.1818401937046005</v>
       </c>
       <c r="H5">
-        <v>-0.1094339622641509</v>
+        <v>-0.1818401937046005</v>
       </c>
       <c r="I5">
-        <v>-0.2233490566037736</v>
+        <v>-0.2469733656174334</v>
       </c>
       <c r="J5">
-        <v>-0.2233490566037736</v>
+        <v>-0.2469733656174334</v>
       </c>
       <c r="K5">
-        <v>-8.449999999999999</v>
+        <v>-11.1</v>
       </c>
       <c r="L5">
-        <v>-0.1992924528301887</v>
+        <v>-0.2687651331719129</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1014,73 +1016,8845 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>5.04</v>
+        <v>3.18</v>
       </c>
       <c r="V5">
-        <v>0.04577656675749319</v>
+        <v>0.02619439868204283</v>
       </c>
       <c r="W5">
-        <v>-0.1459412780656304</v>
+        <v>-0.2142857142857143</v>
       </c>
       <c r="X5">
-        <v>0.121661062518394</v>
+        <v>0.09448878157836979</v>
       </c>
       <c r="Y5">
-        <v>-0.2676023405840244</v>
+        <v>-0.3087744958640841</v>
       </c>
       <c r="Z5">
-        <v>1.028128031037827</v>
+        <v>1.058702896693156</v>
       </c>
       <c r="AA5">
-        <v>-0.229631425800194</v>
+        <v>-0.2614714175852346</v>
       </c>
       <c r="AB5">
-        <v>0.1159382626403812</v>
+        <v>0.0909383760389251</v>
       </c>
       <c r="AC5">
-        <v>-0.3455696884405752</v>
+        <v>-0.3524097936241597</v>
       </c>
       <c r="AD5">
-        <v>8.85</v>
+        <v>8.84</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>8.85</v>
+        <v>8.84</v>
       </c>
       <c r="AG5">
-        <v>3.81</v>
+        <v>5.66</v>
       </c>
       <c r="AH5">
-        <v>0.07440100882723834</v>
+        <v>0.06787469287469287</v>
       </c>
       <c r="AI5">
-        <v>0.1410358565737052</v>
+        <v>0.1749109616145627</v>
       </c>
       <c r="AJ5">
-        <v>0.03344745851988411</v>
+        <v>0.04454588383440894</v>
       </c>
       <c r="AK5">
-        <v>0.06601975394212441</v>
+        <v>0.1195101351351351</v>
       </c>
       <c r="AL5">
-        <v>0.169</v>
+        <v>0.614</v>
       </c>
       <c r="AM5">
-        <v>-0.356</v>
+        <v>0.16</v>
       </c>
       <c r="AN5">
-        <v>-1.2882096069869</v>
+        <v>-1.20600272851296</v>
       </c>
       <c r="AO5">
-        <v>-56.03550295857988</v>
+        <v>-16.61237785016286</v>
       </c>
       <c r="AP5">
-        <v>-0.5545851528384279</v>
+        <v>-0.7721691678035471</v>
       </c>
       <c r="AQ5">
-        <v>26.60112359550562</v>
+        <v>-63.75000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Naseej International Trading Company (SASE:1213)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SASE:1213</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Furn/Home Furnishings</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.690763052208835</v>
+      </c>
+      <c r="F2">
+        <v>4.67437968420287</v>
+      </c>
+      <c r="G2">
+        <v>9.669724770642199</v>
+      </c>
+      <c r="H2">
+        <v>4.12844036697248</v>
+      </c>
+      <c r="I2">
+        <v>0.234222222222222</v>
+      </c>
+      <c r="J2">
+        <v>0.1</v>
+      </c>
+      <c r="K2">
+        <v>172.3</v>
+      </c>
+      <c r="L2">
+        <v>203.697095189233</v>
+      </c>
+      <c r="M2">
+        <v>224.352</v>
+      </c>
+      <c r="N2">
+        <v>225.549095189233</v>
+      </c>
+      <c r="O2">
+        <v>52.7</v>
+      </c>
+      <c r="P2">
+        <v>22.5</v>
+      </c>
+      <c r="Q2">
+        <v>0.0908390103399027</v>
+      </c>
+      <c r="R2">
+        <v>0.0905628148230106</v>
+      </c>
+      <c r="S2">
+        <v>0.0468301443094471</v>
+      </c>
+      <c r="T2">
+        <v>0.04072</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.104299644349218</v>
+      </c>
+      <c r="X2">
+        <v>0.0961009053589006</v>
+      </c>
+      <c r="Y2">
+        <v>1.16312437464853</v>
+      </c>
+      <c r="Z2">
+        <v>1.01753345952575</v>
+      </c>
+      <c r="AA2">
+        <v>52.7</v>
+      </c>
+      <c r="AB2">
+        <v>0.05853768038680883</v>
+      </c>
+      <c r="AC2">
+        <v>0.6907630522088352</v>
+      </c>
+      <c r="AD2">
+        <v>52.7</v>
+      </c>
+      <c r="AE2">
+        <v>2.49</v>
+      </c>
+      <c r="AF2">
+        <v>3.73</v>
+      </c>
+      <c r="AG2">
+        <v>5.45</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>172.3</v>
+      </c>
+      <c r="AK2">
+        <v>0.05631353428476683</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.2</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>3.928</v>
+      </c>
+      <c r="AR2">
+        <v>2.49</v>
+      </c>
+      <c r="AS2">
+        <v>52.7</v>
+      </c>
+      <c r="AT2">
+        <v>0.648</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.09142328043164341</v>
+      </c>
+      <c r="C2">
+        <v>222.5090461380018</v>
+      </c>
+      <c r="D2">
+        <v>221.8610461380018</v>
+      </c>
+      <c r="E2">
+        <v>-52.7</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.648</v>
+      </c>
+      <c r="H2">
+        <v>172.3</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K2">
+        <v>3.73</v>
+      </c>
+      <c r="L2">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="O2">
+        <v>1.070666666666667</v>
+      </c>
+      <c r="P2">
+        <v>4.282666666666667</v>
+      </c>
+      <c r="Q2">
+        <v>8.012666666666668</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.09142328043164341</v>
+      </c>
+      <c r="T2">
+        <v>0.9344695036460948</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.2</v>
+      </c>
+      <c r="W2">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.09128763387078014</v>
+      </c>
+      <c r="C3">
+        <v>220.8324133424035</v>
+      </c>
+      <c r="D3">
+        <v>222.4344133424035</v>
+      </c>
+      <c r="E3">
+        <v>-50.45</v>
+      </c>
+      <c r="F3">
+        <v>2.25</v>
+      </c>
+      <c r="G3">
+        <v>0.648</v>
+      </c>
+      <c r="H3">
+        <v>172.3</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K3">
+        <v>3.73</v>
+      </c>
+      <c r="L3">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M3">
+        <v>0.100575</v>
+      </c>
+      <c r="N3">
+        <v>5.252758333333333</v>
+      </c>
+      <c r="O3">
+        <v>1.050551666666667</v>
+      </c>
+      <c r="P3">
+        <v>4.202206666666667</v>
+      </c>
+      <c r="Q3">
+        <v>7.932206666666668</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.09184851906139407</v>
+      </c>
+      <c r="T3">
+        <v>0.942020772362427</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.2</v>
+      </c>
+      <c r="W3">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>53.22727649349573</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.09115198730991683</v>
+      </c>
+      <c r="C4">
+        <v>219.1587517917718</v>
+      </c>
+      <c r="D4">
+        <v>223.0107517917718</v>
+      </c>
+      <c r="E4">
+        <v>-48.2</v>
+      </c>
+      <c r="F4">
+        <v>4.5</v>
+      </c>
+      <c r="G4">
+        <v>0.648</v>
+      </c>
+      <c r="H4">
+        <v>172.3</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K4">
+        <v>3.73</v>
+      </c>
+      <c r="L4">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M4">
+        <v>0.20115</v>
+      </c>
+      <c r="N4">
+        <v>5.152183333333333</v>
+      </c>
+      <c r="O4">
+        <v>1.030436666666667</v>
+      </c>
+      <c r="P4">
+        <v>4.121746666666667</v>
+      </c>
+      <c r="Q4">
+        <v>7.851746666666667</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.09228243603052738</v>
+      </c>
+      <c r="T4">
+        <v>0.9497261486035821</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.2</v>
+      </c>
+      <c r="W4">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>26.61363824674786</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.09101634074905354</v>
+      </c>
+      <c r="C5">
+        <v>217.4880846420278</v>
+      </c>
+      <c r="D5">
+        <v>223.5900846420278</v>
+      </c>
+      <c r="E5">
+        <v>-45.95</v>
+      </c>
+      <c r="F5">
+        <v>6.75</v>
+      </c>
+      <c r="G5">
+        <v>0.648</v>
+      </c>
+      <c r="H5">
+        <v>172.3</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K5">
+        <v>3.73</v>
+      </c>
+      <c r="L5">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M5">
+        <v>0.301725</v>
+      </c>
+      <c r="N5">
+        <v>5.051608333333333</v>
+      </c>
+      <c r="O5">
+        <v>1.010321666666667</v>
+      </c>
+      <c r="P5">
+        <v>4.041286666666666</v>
+      </c>
+      <c r="Q5">
+        <v>7.771286666666667</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.09272529974129232</v>
+      </c>
+      <c r="T5">
+        <v>0.9575903985816682</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.2</v>
+      </c>
+      <c r="W5">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>17.74242549783191</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.09088069418819027</v>
+      </c>
+      <c r="C6">
+        <v>215.8204352903358</v>
+      </c>
+      <c r="D6">
+        <v>224.1724352903358</v>
+      </c>
+      <c r="E6">
+        <v>-43.7</v>
+      </c>
+      <c r="F6">
+        <v>9</v>
+      </c>
+      <c r="G6">
+        <v>0.648</v>
+      </c>
+      <c r="H6">
+        <v>172.3</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K6">
+        <v>3.73</v>
+      </c>
+      <c r="L6">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M6">
+        <v>0.4023</v>
+      </c>
+      <c r="N6">
+        <v>4.951033333333333</v>
+      </c>
+      <c r="O6">
+        <v>0.9902066666666667</v>
+      </c>
+      <c r="P6">
+        <v>3.960826666666667</v>
+      </c>
+      <c r="Q6">
+        <v>7.690826666666667</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.09317738977936486</v>
+      </c>
+      <c r="T6">
+        <v>0.9656184871009648</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.2</v>
+      </c>
+      <c r="W6">
+        <v>0.03576000000000001</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>13.30681912337393</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.09078904762732697</v>
+      </c>
+      <c r="C7">
+        <v>213.9656076135908</v>
+      </c>
+      <c r="D7">
+        <v>224.5676076135908</v>
+      </c>
+      <c r="E7">
+        <v>-41.45</v>
+      </c>
+      <c r="F7">
+        <v>11.25</v>
+      </c>
+      <c r="G7">
+        <v>0.648</v>
+      </c>
+      <c r="H7">
+        <v>172.3</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K7">
+        <v>3.73</v>
+      </c>
+      <c r="L7">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M7">
+        <v>0.51525</v>
+      </c>
+      <c r="N7">
+        <v>4.838083333333334</v>
+      </c>
+      <c r="O7">
+        <v>0.9676166666666668</v>
+      </c>
+      <c r="P7">
+        <v>3.870466666666667</v>
+      </c>
+      <c r="Q7">
+        <v>7.600466666666668</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.09363899750244944</v>
+      </c>
+      <c r="T7">
+        <v>0.9738155880101408</v>
+      </c>
+      <c r="U7">
+        <v>0.0458</v>
+      </c>
+      <c r="V7">
+        <v>0.2</v>
+      </c>
+      <c r="W7">
+        <v>0.03664</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>10.38977842471292</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.09076780106646368</v>
+      </c>
+      <c r="C8">
+        <v>211.8074200290706</v>
+      </c>
+      <c r="D8">
+        <v>224.6594200290706</v>
+      </c>
+      <c r="E8">
+        <v>-39.2</v>
+      </c>
+      <c r="F8">
+        <v>13.5</v>
+      </c>
+      <c r="G8">
+        <v>0.648</v>
+      </c>
+      <c r="H8">
+        <v>172.3</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K8">
+        <v>3.73</v>
+      </c>
+      <c r="L8">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M8">
+        <v>0.648</v>
+      </c>
+      <c r="N8">
+        <v>4.705333333333334</v>
+      </c>
+      <c r="O8">
+        <v>0.9410666666666668</v>
+      </c>
+      <c r="P8">
+        <v>3.764266666666667</v>
+      </c>
+      <c r="Q8">
+        <v>7.494266666666667</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.09411042666645072</v>
+      </c>
+      <c r="T8">
+        <v>0.9821870953216402</v>
+      </c>
+      <c r="U8">
+        <v>0.048</v>
+      </c>
+      <c r="V8">
+        <v>0.2</v>
+      </c>
+      <c r="W8">
+        <v>0.0384</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>8.261316872427983</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.09074255450560038</v>
+      </c>
+      <c r="C9">
+        <v>209.6666152308712</v>
+      </c>
+      <c r="D9">
+        <v>224.7686152308712</v>
+      </c>
+      <c r="E9">
+        <v>-36.95</v>
+      </c>
+      <c r="F9">
+        <v>15.75</v>
+      </c>
+      <c r="G9">
+        <v>0.648</v>
+      </c>
+      <c r="H9">
+        <v>172.3</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K9">
+        <v>3.73</v>
+      </c>
+      <c r="L9">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M9">
+        <v>0.7796250000000001</v>
+      </c>
+      <c r="N9">
+        <v>4.573708333333333</v>
+      </c>
+      <c r="O9">
+        <v>0.9147416666666667</v>
+      </c>
+      <c r="P9">
+        <v>3.658966666666667</v>
+      </c>
+      <c r="Q9">
+        <v>7.388966666666667</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.09459199409204344</v>
+      </c>
+      <c r="T9">
+        <v>0.9907386350484404</v>
+      </c>
+      <c r="U9">
+        <v>0.0495</v>
+      </c>
+      <c r="V9">
+        <v>0.2</v>
+      </c>
+      <c r="W9">
+        <v>0.0396</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>6.86654908877131</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.09073490794473711</v>
+      </c>
+      <c r="C10">
+        <v>207.4497087120101</v>
+      </c>
+      <c r="D10">
+        <v>224.8017087120101</v>
+      </c>
+      <c r="E10">
+        <v>-34.7</v>
+      </c>
+      <c r="F10">
+        <v>18</v>
+      </c>
+      <c r="G10">
+        <v>0.648</v>
+      </c>
+      <c r="H10">
+        <v>172.3</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K10">
+        <v>3.73</v>
+      </c>
+      <c r="L10">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M10">
+        <v>0.9162</v>
+      </c>
+      <c r="N10">
+        <v>4.437133333333334</v>
+      </c>
+      <c r="O10">
+        <v>0.8874266666666668</v>
+      </c>
+      <c r="P10">
+        <v>3.549706666666667</v>
+      </c>
+      <c r="Q10">
+        <v>7.279706666666668</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.09508403037471425</v>
+      </c>
+      <c r="T10">
+        <v>0.9994760778127797</v>
+      </c>
+      <c r="U10">
+        <v>0.0509</v>
+      </c>
+      <c r="V10">
+        <v>0.2</v>
+      </c>
+      <c r="W10">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>5.842974605253584</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.09064886138387382</v>
+      </c>
+      <c r="C11">
+        <v>205.5727817823644</v>
+      </c>
+      <c r="D11">
+        <v>225.1747817823644</v>
+      </c>
+      <c r="E11">
+        <v>-32.45</v>
+      </c>
+      <c r="F11">
+        <v>20.25</v>
+      </c>
+      <c r="G11">
+        <v>0.648</v>
+      </c>
+      <c r="H11">
+        <v>172.3</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K11">
+        <v>3.73</v>
+      </c>
+      <c r="L11">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M11">
+        <v>1.030725</v>
+      </c>
+      <c r="N11">
+        <v>4.322608333333333</v>
+      </c>
+      <c r="O11">
+        <v>0.8645216666666666</v>
+      </c>
+      <c r="P11">
+        <v>3.458086666666667</v>
+      </c>
+      <c r="Q11">
+        <v>7.188086666666667</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.09558688064161959</v>
+      </c>
+      <c r="T11">
+        <v>1.008405552286225</v>
+      </c>
+      <c r="U11">
+        <v>0.0509</v>
+      </c>
+      <c r="V11">
+        <v>0.2</v>
+      </c>
+      <c r="W11">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>5.193755204669851</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.09056281482301057</v>
+      </c>
+      <c r="C12">
+        <v>203.6970951892329</v>
+      </c>
+      <c r="D12">
+        <v>225.5490951892329</v>
+      </c>
+      <c r="E12">
+        <v>-30.2</v>
+      </c>
+      <c r="F12">
+        <v>22.5</v>
+      </c>
+      <c r="G12">
+        <v>0.648</v>
+      </c>
+      <c r="H12">
+        <v>172.3</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K12">
+        <v>3.73</v>
+      </c>
+      <c r="L12">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M12">
+        <v>1.14525</v>
+      </c>
+      <c r="N12">
+        <v>4.208083333333334</v>
+      </c>
+      <c r="O12">
+        <v>0.8416166666666668</v>
+      </c>
+      <c r="P12">
+        <v>3.366466666666667</v>
+      </c>
+      <c r="Q12">
+        <v>7.096466666666667</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.09610090535890062</v>
+      </c>
+      <c r="T12">
+        <v>1.017533459525748</v>
+      </c>
+      <c r="U12">
+        <v>0.0509</v>
+      </c>
+      <c r="V12">
+        <v>0.2</v>
+      </c>
+      <c r="W12">
+        <v>0.04072000000000001</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>4.674379684202867</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.09070556826214725</v>
+      </c>
+      <c r="C13">
+        <v>200.8267781382796</v>
+      </c>
+      <c r="D13">
+        <v>224.9287781382797</v>
+      </c>
+      <c r="E13">
+        <v>-27.95</v>
+      </c>
+      <c r="F13">
+        <v>24.75</v>
+      </c>
+      <c r="G13">
+        <v>0.648</v>
+      </c>
+      <c r="H13">
+        <v>172.3</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K13">
+        <v>3.73</v>
+      </c>
+      <c r="L13">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M13">
+        <v>1.324125</v>
+      </c>
+      <c r="N13">
+        <v>4.029208333333333</v>
+      </c>
+      <c r="O13">
+        <v>0.8058416666666667</v>
+      </c>
+      <c r="P13">
+        <v>3.223366666666666</v>
+      </c>
+      <c r="Q13">
+        <v>6.953366666666667</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.09662648119342387</v>
+      </c>
+      <c r="T13">
+        <v>1.02686648827627</v>
+      </c>
+      <c r="U13">
+        <v>0.0535</v>
+      </c>
+      <c r="V13">
+        <v>0.2</v>
+      </c>
+      <c r="W13">
+        <v>0.0428</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>4.042921426098996</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.09089952170128397</v>
+      </c>
+      <c r="C14">
+        <v>197.7394247681111</v>
+      </c>
+      <c r="D14">
+        <v>224.0914247681111</v>
+      </c>
+      <c r="E14">
+        <v>-25.7</v>
+      </c>
+      <c r="F14">
+        <v>27</v>
+      </c>
+      <c r="G14">
+        <v>0.648</v>
+      </c>
+      <c r="H14">
+        <v>172.3</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K14">
+        <v>3.73</v>
+      </c>
+      <c r="L14">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M14">
+        <v>1.5174</v>
+      </c>
+      <c r="N14">
+        <v>3.835933333333333</v>
+      </c>
+      <c r="O14">
+        <v>0.7671866666666667</v>
+      </c>
+      <c r="P14">
+        <v>3.068746666666667</v>
+      </c>
+      <c r="Q14">
+        <v>6.798746666666667</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.09716400193327723</v>
+      </c>
+      <c r="T14">
+        <v>1.036411631316578</v>
+      </c>
+      <c r="U14">
+        <v>0.0562</v>
+      </c>
+      <c r="V14">
+        <v>0.2</v>
+      </c>
+      <c r="W14">
+        <v>0.04496</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>3.527964500680989</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.09134467514042068</v>
+      </c>
+      <c r="C15">
+        <v>193.5909437488645</v>
+      </c>
+      <c r="D15">
+        <v>222.1929437488645</v>
+      </c>
+      <c r="E15">
+        <v>-23.45</v>
+      </c>
+      <c r="F15">
+        <v>29.25</v>
+      </c>
+      <c r="G15">
+        <v>0.648</v>
+      </c>
+      <c r="H15">
+        <v>172.3</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K15">
+        <v>3.73</v>
+      </c>
+      <c r="L15">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M15">
+        <v>1.781325</v>
+      </c>
+      <c r="N15">
+        <v>3.572008333333334</v>
+      </c>
+      <c r="O15">
+        <v>0.7144016666666668</v>
+      </c>
+      <c r="P15">
+        <v>2.857606666666667</v>
+      </c>
+      <c r="Q15">
+        <v>6.587606666666668</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.09771387947174791</v>
+      </c>
+      <c r="T15">
+        <v>1.046176202932525</v>
+      </c>
+      <c r="U15">
+        <v>0.0609</v>
+      </c>
+      <c r="V15">
+        <v>0.2</v>
+      </c>
+      <c r="W15">
+        <v>0.04872000000000001</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>3.005253579966224</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.09290662857955741</v>
+      </c>
+      <c r="C16">
+        <v>184.926664357382</v>
+      </c>
+      <c r="D16">
+        <v>215.778664357382</v>
+      </c>
+      <c r="E16">
+        <v>-21.2</v>
+      </c>
+      <c r="F16">
+        <v>31.5</v>
+      </c>
+      <c r="G16">
+        <v>0.648</v>
+      </c>
+      <c r="H16">
+        <v>172.3</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K16">
+        <v>3.73</v>
+      </c>
+      <c r="L16">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M16">
+        <v>2.35935</v>
+      </c>
+      <c r="N16">
+        <v>2.993983333333333</v>
+      </c>
+      <c r="O16">
+        <v>0.5987966666666668</v>
+      </c>
+      <c r="P16">
+        <v>2.395186666666667</v>
+      </c>
+      <c r="Q16">
+        <v>6.125186666666667</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.09827654485995047</v>
+      </c>
+      <c r="T16">
+        <v>1.056167857609307</v>
+      </c>
+      <c r="U16">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V16">
+        <v>0.2</v>
+      </c>
+      <c r="W16">
+        <v>0.05992</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>2.268986514647396</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.09301258201869408</v>
+      </c>
+      <c r="C17">
+        <v>182.2549450676957</v>
+      </c>
+      <c r="D17">
+        <v>215.3569450676957</v>
+      </c>
+      <c r="E17">
+        <v>-18.95</v>
+      </c>
+      <c r="F17">
+        <v>33.75</v>
+      </c>
+      <c r="G17">
+        <v>0.648</v>
+      </c>
+      <c r="H17">
+        <v>172.3</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K17">
+        <v>3.73</v>
+      </c>
+      <c r="L17">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M17">
+        <v>2.527875</v>
+      </c>
+      <c r="N17">
+        <v>2.825458333333334</v>
+      </c>
+      <c r="O17">
+        <v>0.5650916666666668</v>
+      </c>
+      <c r="P17">
+        <v>2.260366666666667</v>
+      </c>
+      <c r="Q17">
+        <v>5.990366666666668</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.09885244943375776</v>
+      </c>
+      <c r="T17">
+        <v>1.06639461004319</v>
+      </c>
+      <c r="U17">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V17">
+        <v>0.2</v>
+      </c>
+      <c r="W17">
+        <v>0.05992</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>2.117720747004237</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.09520493545783082</v>
+      </c>
+      <c r="C18">
+        <v>171.6344268616404</v>
+      </c>
+      <c r="D18">
+        <v>206.9864268616404</v>
+      </c>
+      <c r="E18">
+        <v>-16.7</v>
+      </c>
+      <c r="F18">
+        <v>36</v>
+      </c>
+      <c r="G18">
+        <v>0.648</v>
+      </c>
+      <c r="H18">
+        <v>172.3</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K18">
+        <v>3.73</v>
+      </c>
+      <c r="L18">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M18">
+        <v>3.2832</v>
+      </c>
+      <c r="N18">
+        <v>2.070133333333334</v>
+      </c>
+      <c r="O18">
+        <v>0.4140266666666668</v>
+      </c>
+      <c r="P18">
+        <v>1.656106666666667</v>
+      </c>
+      <c r="Q18">
+        <v>5.386106666666667</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.09944206602122715</v>
+      </c>
+      <c r="T18">
+        <v>1.076864856582642</v>
+      </c>
+      <c r="U18">
+        <v>0.0912</v>
+      </c>
+      <c r="V18">
+        <v>0.2</v>
+      </c>
+      <c r="W18">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>1.630523066926576</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.09544128889696753</v>
+      </c>
+      <c r="C19">
+        <v>168.5207114555105</v>
+      </c>
+      <c r="D19">
+        <v>206.1227114555105</v>
+      </c>
+      <c r="E19">
+        <v>-14.45</v>
+      </c>
+      <c r="F19">
+        <v>38.25</v>
+      </c>
+      <c r="G19">
+        <v>0.648</v>
+      </c>
+      <c r="H19">
+        <v>172.3</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K19">
+        <v>3.73</v>
+      </c>
+      <c r="L19">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M19">
+        <v>3.4884</v>
+      </c>
+      <c r="N19">
+        <v>1.864933333333334</v>
+      </c>
+      <c r="O19">
+        <v>0.3729866666666667</v>
+      </c>
+      <c r="P19">
+        <v>1.491946666666667</v>
+      </c>
+      <c r="Q19">
+        <v>5.221946666666668</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1000458902373103</v>
+      </c>
+      <c r="T19">
+        <v>1.087587398219431</v>
+      </c>
+      <c r="U19">
+        <v>0.0912</v>
+      </c>
+      <c r="V19">
+        <v>0.2</v>
+      </c>
+      <c r="W19">
+        <v>0.07296000000000001</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>1.53460994534266</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1062697270827343</v>
+      </c>
+      <c r="C20">
+        <v>133.1894002336394</v>
+      </c>
+      <c r="D20">
+        <v>173.0414002336395</v>
+      </c>
+      <c r="E20">
+        <v>-12.2</v>
+      </c>
+      <c r="F20">
+        <v>40.5</v>
+      </c>
+      <c r="G20">
+        <v>0.648</v>
+      </c>
+      <c r="H20">
+        <v>172.3</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K20">
+        <v>3.73</v>
+      </c>
+      <c r="L20">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M20">
+        <v>6.342300000000001</v>
+      </c>
+      <c r="N20">
+        <v>-0.9889666666666672</v>
+      </c>
+      <c r="O20">
+        <v>-0.1977933333333335</v>
+      </c>
+      <c r="P20">
+        <v>-0.7911733333333337</v>
+      </c>
+      <c r="Q20">
+        <v>2.938826666666666</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1010246897576254</v>
+      </c>
+      <c r="T20">
+        <v>1.10496864648855</v>
+      </c>
+      <c r="U20">
+        <v>0.1566</v>
+      </c>
+      <c r="V20">
+        <v>0.168813627022794</v>
+      </c>
+      <c r="W20">
+        <v>0.1301637860082305</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.8440681351139702</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1177654857903319</v>
+      </c>
+      <c r="C21">
+        <v>105.7481136404998</v>
+      </c>
+      <c r="D21">
+        <v>147.8501136404998</v>
+      </c>
+      <c r="E21">
+        <v>-9.950000000000003</v>
+      </c>
+      <c r="F21">
+        <v>42.75</v>
+      </c>
+      <c r="G21">
+        <v>0.648</v>
+      </c>
+      <c r="H21">
+        <v>172.3</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K21">
+        <v>3.73</v>
+      </c>
+      <c r="L21">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M21">
+        <v>8.9262</v>
+      </c>
+      <c r="N21">
+        <v>-3.572866666666666</v>
+      </c>
+      <c r="O21">
+        <v>-0.7145733333333333</v>
+      </c>
+      <c r="P21">
+        <v>-2.858293333333333</v>
+      </c>
+      <c r="Q21">
+        <v>0.8717066666666673</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1022864250726549</v>
+      </c>
+      <c r="T21">
+        <v>1.12737418950862</v>
+      </c>
+      <c r="U21">
+        <v>0.2088</v>
+      </c>
+      <c r="V21">
+        <v>0.1199465244635642</v>
+      </c>
+      <c r="W21">
+        <v>0.1837551656920078</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.599732622317821</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1194654857903319</v>
+      </c>
+      <c r="C22">
+        <v>100.3822185246859</v>
+      </c>
+      <c r="D22">
+        <v>144.7342185246859</v>
+      </c>
+      <c r="E22">
+        <v>-7.700000000000003</v>
+      </c>
+      <c r="F22">
+        <v>45</v>
+      </c>
+      <c r="G22">
+        <v>0.648</v>
+      </c>
+      <c r="H22">
+        <v>172.3</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K22">
+        <v>3.73</v>
+      </c>
+      <c r="L22">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M22">
+        <v>9.396000000000001</v>
+      </c>
+      <c r="N22">
+        <v>-4.042666666666667</v>
+      </c>
+      <c r="O22">
+        <v>-0.8085333333333335</v>
+      </c>
+      <c r="P22">
+        <v>-3.234133333333334</v>
+      </c>
+      <c r="Q22">
+        <v>0.4958666666666667</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1030800053860631</v>
+      </c>
+      <c r="T22">
+        <v>1.141466366877478</v>
+      </c>
+      <c r="U22">
+        <v>0.2088</v>
+      </c>
+      <c r="V22">
+        <v>0.113949198240386</v>
+      </c>
+      <c r="W22">
+        <v>0.1850074074074074</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.5697459912019298</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1211654857903319</v>
+      </c>
+      <c r="C23">
+        <v>95.1449457716507</v>
+      </c>
+      <c r="D23">
+        <v>141.7469457716507</v>
+      </c>
+      <c r="E23">
+        <v>-5.450000000000003</v>
+      </c>
+      <c r="F23">
+        <v>47.25</v>
+      </c>
+      <c r="G23">
+        <v>0.648</v>
+      </c>
+      <c r="H23">
+        <v>172.3</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K23">
+        <v>3.73</v>
+      </c>
+      <c r="L23">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M23">
+        <v>9.8658</v>
+      </c>
+      <c r="N23">
+        <v>-4.512466666666667</v>
+      </c>
+      <c r="O23">
+        <v>-0.9024933333333334</v>
+      </c>
+      <c r="P23">
+        <v>-3.609973333333333</v>
+      </c>
+      <c r="Q23">
+        <v>0.1200266666666669</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.103893676340317</v>
+      </c>
+      <c r="T23">
+        <v>1.155915308230357</v>
+      </c>
+      <c r="U23">
+        <v>0.2088</v>
+      </c>
+      <c r="V23">
+        <v>0.1085230459432248</v>
+      </c>
+      <c r="W23">
+        <v>0.1861403880070547</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.5426152297161237</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1228654857903319</v>
+      </c>
+      <c r="C24">
+        <v>90.02849224977598</v>
+      </c>
+      <c r="D24">
+        <v>138.880492249776</v>
+      </c>
+      <c r="E24">
+        <v>-3.200000000000003</v>
+      </c>
+      <c r="F24">
+        <v>49.5</v>
+      </c>
+      <c r="G24">
+        <v>0.648</v>
+      </c>
+      <c r="H24">
+        <v>172.3</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K24">
+        <v>3.73</v>
+      </c>
+      <c r="L24">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M24">
+        <v>10.3356</v>
+      </c>
+      <c r="N24">
+        <v>-4.982266666666668</v>
+      </c>
+      <c r="O24">
+        <v>-0.9964533333333336</v>
+      </c>
+      <c r="P24">
+        <v>-3.985813333333334</v>
+      </c>
+      <c r="Q24">
+        <v>-0.2558133333333337</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1047282106523724</v>
+      </c>
+      <c r="T24">
+        <v>1.170734735258951</v>
+      </c>
+      <c r="U24">
+        <v>0.2088</v>
+      </c>
+      <c r="V24">
+        <v>0.1035901802185327</v>
+      </c>
+      <c r="W24">
+        <v>0.1871703703703704</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.5179509010926635</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1316161486198285</v>
+      </c>
+      <c r="C25">
+        <v>74.68490477234128</v>
+      </c>
+      <c r="D25">
+        <v>125.7869047723413</v>
+      </c>
+      <c r="E25">
+        <v>-0.9500000000000028</v>
+      </c>
+      <c r="F25">
+        <v>51.75</v>
+      </c>
+      <c r="G25">
+        <v>0.648</v>
+      </c>
+      <c r="H25">
+        <v>172.3</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K25">
+        <v>3.73</v>
+      </c>
+      <c r="L25">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M25">
+        <v>12.3579</v>
+      </c>
+      <c r="N25">
+        <v>-7.004566666666667</v>
+      </c>
+      <c r="O25">
+        <v>-1.400913333333333</v>
+      </c>
+      <c r="P25">
+        <v>-5.603653333333334</v>
+      </c>
+      <c r="Q25">
+        <v>-1.873653333333333</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1057800871926585</v>
+      </c>
+      <c r="T25">
+        <v>1.189413664820839</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>0.08663823680938239</v>
+      </c>
+      <c r="W25">
+        <v>0.2181107890499195</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.4331911840469119</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1336161486198285</v>
+      </c>
+      <c r="C26">
+        <v>69.7816245747519</v>
+      </c>
+      <c r="D26">
+        <v>123.1336245747519</v>
+      </c>
+      <c r="E26">
+        <v>1.299999999999997</v>
+      </c>
+      <c r="F26">
+        <v>54</v>
+      </c>
+      <c r="G26">
+        <v>0.648</v>
+      </c>
+      <c r="H26">
+        <v>172.3</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K26">
+        <v>3.73</v>
+      </c>
+      <c r="L26">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M26">
+        <v>12.8952</v>
+      </c>
+      <c r="N26">
+        <v>-7.541866666666667</v>
+      </c>
+      <c r="O26">
+        <v>-1.508373333333334</v>
+      </c>
+      <c r="P26">
+        <v>-6.033493333333334</v>
+      </c>
+      <c r="Q26">
+        <v>-2.303493333333334</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.106661404129404</v>
+      </c>
+      <c r="T26">
+        <v>1.205063844621114</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0.08302831027565813</v>
+      </c>
+      <c r="W26">
+        <v>0.2189728395061729</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.4151415513782906</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1356161486198285</v>
+      </c>
+      <c r="C27">
+        <v>64.98796576720595</v>
+      </c>
+      <c r="D27">
+        <v>120.589965767206</v>
+      </c>
+      <c r="E27">
+        <v>3.549999999999997</v>
+      </c>
+      <c r="F27">
+        <v>56.25</v>
+      </c>
+      <c r="G27">
+        <v>0.648</v>
+      </c>
+      <c r="H27">
+        <v>172.3</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K27">
+        <v>3.73</v>
+      </c>
+      <c r="L27">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M27">
+        <v>13.4325</v>
+      </c>
+      <c r="N27">
+        <v>-8.079166666666667</v>
+      </c>
+      <c r="O27">
+        <v>-1.615833333333334</v>
+      </c>
+      <c r="P27">
+        <v>-6.463333333333334</v>
+      </c>
+      <c r="Q27">
+        <v>-2.733333333333333</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1075662228511294</v>
+      </c>
+      <c r="T27">
+        <v>1.221131362549395</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0.0797071778646318</v>
+      </c>
+      <c r="W27">
+        <v>0.2197659259259259</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.398535889323159</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1376161486198285</v>
+      </c>
+      <c r="C28">
+        <v>60.29727226818797</v>
+      </c>
+      <c r="D28">
+        <v>118.149272268188</v>
+      </c>
+      <c r="E28">
+        <v>5.799999999999997</v>
+      </c>
+      <c r="F28">
+        <v>58.5</v>
+      </c>
+      <c r="G28">
+        <v>0.648</v>
+      </c>
+      <c r="H28">
+        <v>172.3</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K28">
+        <v>3.73</v>
+      </c>
+      <c r="L28">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M28">
+        <v>13.9698</v>
+      </c>
+      <c r="N28">
+        <v>-8.616466666666668</v>
+      </c>
+      <c r="O28">
+        <v>-1.723293333333334</v>
+      </c>
+      <c r="P28">
+        <v>-6.893173333333334</v>
+      </c>
+      <c r="Q28">
+        <v>-3.163173333333334</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1084954961329014</v>
+      </c>
+      <c r="T28">
+        <v>1.237633137718982</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0.07664151717753058</v>
+      </c>
+      <c r="W28">
+        <v>0.2204980056980057</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.3832075858876529</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1396161486198286</v>
+      </c>
+      <c r="C29">
+        <v>55.70341617200392</v>
+      </c>
+      <c r="D29">
+        <v>115.8054161720039</v>
+      </c>
+      <c r="E29">
+        <v>8.050000000000004</v>
+      </c>
+      <c r="F29">
+        <v>60.75000000000001</v>
+      </c>
+      <c r="G29">
+        <v>0.648</v>
+      </c>
+      <c r="H29">
+        <v>172.3</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K29">
+        <v>3.73</v>
+      </c>
+      <c r="L29">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M29">
+        <v>14.5071</v>
+      </c>
+      <c r="N29">
+        <v>-9.153766666666669</v>
+      </c>
+      <c r="O29">
+        <v>-1.830753333333334</v>
+      </c>
+      <c r="P29">
+        <v>-7.323013333333336</v>
+      </c>
+      <c r="Q29">
+        <v>-3.593013333333335</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1094502289566398</v>
+      </c>
+      <c r="T29">
+        <v>1.254587016317872</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0.07380294246725165</v>
+      </c>
+      <c r="W29">
+        <v>0.2211758573388203</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.3690147123362583</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1416161486198285</v>
+      </c>
+      <c r="C30">
+        <v>51.20074637788039</v>
+      </c>
+      <c r="D30">
+        <v>113.5527463778804</v>
+      </c>
+      <c r="E30">
+        <v>10.3</v>
+      </c>
+      <c r="F30">
+        <v>63.00000000000001</v>
+      </c>
+      <c r="G30">
+        <v>0.648</v>
+      </c>
+      <c r="H30">
+        <v>172.3</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K30">
+        <v>3.73</v>
+      </c>
+      <c r="L30">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M30">
+        <v>15.0444</v>
+      </c>
+      <c r="N30">
+        <v>-9.69106666666667</v>
+      </c>
+      <c r="O30">
+        <v>-1.938213333333334</v>
+      </c>
+      <c r="P30">
+        <v>-7.752853333333336</v>
+      </c>
+      <c r="Q30">
+        <v>-4.022853333333336</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1104314821365931</v>
+      </c>
+      <c r="T30">
+        <v>1.272011835988953</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0.07116712309342124</v>
+      </c>
+      <c r="W30">
+        <v>0.221805291005291</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.3558356154671062</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1436161486198285</v>
+      </c>
+      <c r="C31">
+        <v>46.78404310032079</v>
+      </c>
+      <c r="D31">
+        <v>111.3860431003208</v>
+      </c>
+      <c r="E31">
+        <v>12.55</v>
+      </c>
+      <c r="F31">
+        <v>65.25</v>
+      </c>
+      <c r="G31">
+        <v>0.648</v>
+      </c>
+      <c r="H31">
+        <v>172.3</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K31">
+        <v>3.73</v>
+      </c>
+      <c r="L31">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M31">
+        <v>15.5817</v>
+      </c>
+      <c r="N31">
+        <v>-10.22836666666667</v>
+      </c>
+      <c r="O31">
+        <v>-2.045673333333334</v>
+      </c>
+      <c r="P31">
+        <v>-8.182693333333335</v>
+      </c>
+      <c r="Q31">
+        <v>-4.452693333333334</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.111440376251193</v>
+      </c>
+      <c r="T31">
+        <v>1.28992749565077</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.0687130843660619</v>
+      </c>
+      <c r="W31">
+        <v>0.2223913154533844</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.3435654218303095</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1456161486198285</v>
+      </c>
+      <c r="C32">
+        <v>42.44847748988563</v>
+      </c>
+      <c r="D32">
+        <v>109.3004774898856</v>
+      </c>
+      <c r="E32">
+        <v>14.8</v>
+      </c>
+      <c r="F32">
+        <v>67.5</v>
+      </c>
+      <c r="G32">
+        <v>0.648</v>
+      </c>
+      <c r="H32">
+        <v>172.3</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K32">
+        <v>3.73</v>
+      </c>
+      <c r="L32">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M32">
+        <v>16.119</v>
+      </c>
+      <c r="N32">
+        <v>-10.76566666666667</v>
+      </c>
+      <c r="O32">
+        <v>-2.153133333333333</v>
+      </c>
+      <c r="P32">
+        <v>-8.612533333333333</v>
+      </c>
+      <c r="Q32">
+        <v>-4.882533333333333</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1124780959119244</v>
+      </c>
+      <c r="T32">
+        <v>1.308355031302924</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.0664226482205265</v>
+      </c>
+      <c r="W32">
+        <v>0.2229382716049383</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.3321132411026325</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1476161486198285</v>
+      </c>
+      <c r="C33">
+        <v>38.18957570690215</v>
+      </c>
+      <c r="D33">
+        <v>107.2915757069022</v>
+      </c>
+      <c r="E33">
+        <v>17.05</v>
+      </c>
+      <c r="F33">
+        <v>69.75</v>
+      </c>
+      <c r="G33">
+        <v>0.648</v>
+      </c>
+      <c r="H33">
+        <v>172.3</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K33">
+        <v>3.73</v>
+      </c>
+      <c r="L33">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M33">
+        <v>16.6563</v>
+      </c>
+      <c r="N33">
+        <v>-11.30296666666667</v>
+      </c>
+      <c r="O33">
+        <v>-2.260593333333334</v>
+      </c>
+      <c r="P33">
+        <v>-9.042373333333334</v>
+      </c>
+      <c r="Q33">
+        <v>-5.312373333333333</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1135458944034015</v>
+      </c>
+      <c r="T33">
+        <v>1.327316698423256</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.06427998214889662</v>
+      </c>
+      <c r="W33">
+        <v>0.2234499402628435</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.321399910744483</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1496161486198285</v>
+      </c>
+      <c r="C34">
+        <v>34.00318688554034</v>
+      </c>
+      <c r="D34">
+        <v>105.3551868855403</v>
+      </c>
+      <c r="E34">
+        <v>19.3</v>
+      </c>
+      <c r="F34">
+        <v>72</v>
+      </c>
+      <c r="G34">
+        <v>0.648</v>
+      </c>
+      <c r="H34">
+        <v>172.3</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K34">
+        <v>3.73</v>
+      </c>
+      <c r="L34">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M34">
+        <v>17.1936</v>
+      </c>
+      <c r="N34">
+        <v>-11.84026666666667</v>
+      </c>
+      <c r="O34">
+        <v>-2.368053333333334</v>
+      </c>
+      <c r="P34">
+        <v>-9.472213333333332</v>
+      </c>
+      <c r="Q34">
+        <v>-5.742213333333332</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1146450987328633</v>
+      </c>
+      <c r="T34">
+        <v>1.346836061635363</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.0622712327067436</v>
+      </c>
+      <c r="W34">
+        <v>0.2239296296296296</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.311356163533718</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1516161486198285</v>
+      </c>
+      <c r="C35">
+        <v>29.88545450547886</v>
+      </c>
+      <c r="D35">
+        <v>103.4874545054789</v>
+      </c>
+      <c r="E35">
+        <v>21.55</v>
+      </c>
+      <c r="F35">
+        <v>74.25</v>
+      </c>
+      <c r="G35">
+        <v>0.648</v>
+      </c>
+      <c r="H35">
+        <v>172.3</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K35">
+        <v>3.73</v>
+      </c>
+      <c r="L35">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M35">
+        <v>17.7309</v>
+      </c>
+      <c r="N35">
+        <v>-12.37756666666667</v>
+      </c>
+      <c r="O35">
+        <v>-2.475513333333334</v>
+      </c>
+      <c r="P35">
+        <v>-9.902053333333335</v>
+      </c>
+      <c r="Q35">
+        <v>-6.172053333333334</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1157771151318613</v>
+      </c>
+      <c r="T35">
+        <v>1.36693809240604</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.06038422565502408</v>
+      </c>
+      <c r="W35">
+        <v>0.2243802469135802</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.3019211282751204</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1536161486198285</v>
+      </c>
+      <c r="C36">
+        <v>25.83279075565845</v>
+      </c>
+      <c r="D36">
+        <v>101.6847907556585</v>
+      </c>
+      <c r="E36">
+        <v>23.8</v>
+      </c>
+      <c r="F36">
+        <v>76.5</v>
+      </c>
+      <c r="G36">
+        <v>0.648</v>
+      </c>
+      <c r="H36">
+        <v>172.3</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K36">
+        <v>3.73</v>
+      </c>
+      <c r="L36">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M36">
+        <v>18.2682</v>
+      </c>
+      <c r="N36">
+        <v>-12.91486666666667</v>
+      </c>
+      <c r="O36">
+        <v>-2.582973333333333</v>
+      </c>
+      <c r="P36">
+        <v>-10.33189333333333</v>
+      </c>
+      <c r="Q36">
+        <v>-6.601893333333333</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1169434350581016</v>
+      </c>
+      <c r="T36">
+        <v>1.387649275624313</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.05860821901811162</v>
+      </c>
+      <c r="W36">
+        <v>0.2248043572984749</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.2930410950905581</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1556161486198285</v>
+      </c>
+      <c r="C37">
+        <v>21.84185353153224</v>
+      </c>
+      <c r="D37">
+        <v>99.94385353153226</v>
+      </c>
+      <c r="E37">
+        <v>26.05000000000001</v>
+      </c>
+      <c r="F37">
+        <v>78.75000000000001</v>
+      </c>
+      <c r="G37">
+        <v>0.648</v>
+      </c>
+      <c r="H37">
+        <v>172.3</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K37">
+        <v>3.73</v>
+      </c>
+      <c r="L37">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M37">
+        <v>18.80550000000001</v>
+      </c>
+      <c r="N37">
+        <v>-13.45216666666667</v>
+      </c>
+      <c r="O37">
+        <v>-2.690433333333335</v>
+      </c>
+      <c r="P37">
+        <v>-10.76173333333334</v>
+      </c>
+      <c r="Q37">
+        <v>-7.031733333333337</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1181456417513032</v>
+      </c>
+      <c r="T37">
+        <v>1.408997726018533</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.05693369847473698</v>
+      </c>
+      <c r="W37">
+        <v>0.2252042328042328</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.284668492373685</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1576161486198285</v>
+      </c>
+      <c r="C38">
+        <v>17.90952575551053</v>
+      </c>
+      <c r="D38">
+        <v>98.26152575551053</v>
+      </c>
+      <c r="E38">
+        <v>28.3</v>
+      </c>
+      <c r="F38">
+        <v>81</v>
+      </c>
+      <c r="G38">
+        <v>0.648</v>
+      </c>
+      <c r="H38">
+        <v>172.3</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K38">
+        <v>3.73</v>
+      </c>
+      <c r="L38">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M38">
+        <v>19.3428</v>
+      </c>
+      <c r="N38">
+        <v>-13.98946666666667</v>
+      </c>
+      <c r="O38">
+        <v>-2.797893333333334</v>
+      </c>
+      <c r="P38">
+        <v>-11.19157333333333</v>
+      </c>
+      <c r="Q38">
+        <v>-7.461573333333334</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1193854174036673</v>
+      </c>
+      <c r="T38">
+        <v>1.431013315487573</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.05535220685043876</v>
+      </c>
+      <c r="W38">
+        <v>0.2255818930041152</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.2767610342521938</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1596161486198285</v>
+      </c>
+      <c r="C39">
+        <v>14.03289675139105</v>
+      </c>
+      <c r="D39">
+        <v>96.63489675139105</v>
+      </c>
+      <c r="E39">
+        <v>30.55</v>
+      </c>
+      <c r="F39">
+        <v>83.25</v>
+      </c>
+      <c r="G39">
+        <v>0.648</v>
+      </c>
+      <c r="H39">
+        <v>172.3</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K39">
+        <v>3.73</v>
+      </c>
+      <c r="L39">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M39">
+        <v>19.8801</v>
+      </c>
+      <c r="N39">
+        <v>-14.52676666666667</v>
+      </c>
+      <c r="O39">
+        <v>-2.905353333333334</v>
+      </c>
+      <c r="P39">
+        <v>-11.62141333333333</v>
+      </c>
+      <c r="Q39">
+        <v>-7.891413333333334</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1206645510132493</v>
+      </c>
+      <c r="T39">
+        <v>1.453727812558804</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.05385620125988635</v>
+      </c>
+      <c r="W39">
+        <v>0.2259391391391392</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.2692810062994317</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1616161486198285</v>
+      </c>
+      <c r="C40">
+        <v>10.20924543863869</v>
+      </c>
+      <c r="D40">
+        <v>95.06124543863869</v>
+      </c>
+      <c r="E40">
+        <v>32.8</v>
+      </c>
+      <c r="F40">
+        <v>85.5</v>
+      </c>
+      <c r="G40">
+        <v>0.648</v>
+      </c>
+      <c r="H40">
+        <v>172.3</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K40">
+        <v>3.73</v>
+      </c>
+      <c r="L40">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M40">
+        <v>20.4174</v>
+      </c>
+      <c r="N40">
+        <v>-15.06406666666667</v>
+      </c>
+      <c r="O40">
+        <v>-3.012813333333334</v>
+      </c>
+      <c r="P40">
+        <v>-12.05125333333333</v>
+      </c>
+      <c r="Q40">
+        <v>-8.321253333333333</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.121984946997334</v>
+      </c>
+      <c r="T40">
+        <v>1.47717503534201</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.05243893280567882</v>
+      </c>
+      <c r="W40">
+        <v>0.2262775828460039</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.2621946640283941</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1636161486198285</v>
+      </c>
+      <c r="C41">
+        <v>6.436025142390307</v>
+      </c>
+      <c r="D41">
+        <v>93.53802514239031</v>
+      </c>
+      <c r="E41">
+        <v>35.05</v>
+      </c>
+      <c r="F41">
+        <v>87.75</v>
+      </c>
+      <c r="G41">
+        <v>0.648</v>
+      </c>
+      <c r="H41">
+        <v>172.3</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K41">
+        <v>3.73</v>
+      </c>
+      <c r="L41">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M41">
+        <v>20.9547</v>
+      </c>
+      <c r="N41">
+        <v>-15.60136666666667</v>
+      </c>
+      <c r="O41">
+        <v>-3.120273333333334</v>
+      </c>
+      <c r="P41">
+        <v>-12.48109333333334</v>
+      </c>
+      <c r="Q41">
+        <v>-8.751093333333335</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.123348634653028</v>
+      </c>
+      <c r="T41">
+        <v>1.501391019527945</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.05109434478502039</v>
+      </c>
+      <c r="W41">
+        <v>0.2265986704653371</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.2554717239251019</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1656161486198285</v>
+      </c>
+      <c r="C42">
+        <v>2.71084984081574</v>
+      </c>
+      <c r="D42">
+        <v>92.06284984081574</v>
+      </c>
+      <c r="E42">
+        <v>37.3</v>
+      </c>
+      <c r="F42">
+        <v>90</v>
+      </c>
+      <c r="G42">
+        <v>0.648</v>
+      </c>
+      <c r="H42">
+        <v>172.3</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K42">
+        <v>3.73</v>
+      </c>
+      <c r="L42">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M42">
+        <v>21.492</v>
+      </c>
+      <c r="N42">
+        <v>-16.13866666666667</v>
+      </c>
+      <c r="O42">
+        <v>-3.227733333333333</v>
+      </c>
+      <c r="P42">
+        <v>-12.91093333333333</v>
+      </c>
+      <c r="Q42">
+        <v>-9.180933333333332</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1247577785639118</v>
+      </c>
+      <c r="T42">
+        <v>1.526414203186744</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.04981698616539488</v>
+      </c>
+      <c r="W42">
+        <v>0.2269037037037037</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.2490849308269745</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1676161486198285</v>
+      </c>
+      <c r="C43">
+        <v>-0.9685183063801333</v>
+      </c>
+      <c r="D43">
+        <v>90.63348169361987</v>
+      </c>
+      <c r="E43">
+        <v>39.55</v>
+      </c>
+      <c r="F43">
+        <v>92.25</v>
+      </c>
+      <c r="G43">
+        <v>0.648</v>
+      </c>
+      <c r="H43">
+        <v>172.3</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K43">
+        <v>3.73</v>
+      </c>
+      <c r="L43">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M43">
+        <v>22.0293</v>
+      </c>
+      <c r="N43">
+        <v>-16.67596666666667</v>
+      </c>
+      <c r="O43">
+        <v>-3.335193333333334</v>
+      </c>
+      <c r="P43">
+        <v>-13.34077333333333</v>
+      </c>
+      <c r="Q43">
+        <v>-9.610773333333334</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.126214690064995</v>
+      </c>
+      <c r="T43">
+        <v>1.552285630359401</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.04860193772233646</v>
+      </c>
+      <c r="W43">
+        <v>0.2271938572719061</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.2430096886116824</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1696161486198285</v>
+      </c>
+      <c r="C44">
+        <v>-4.604180285422402</v>
+      </c>
+      <c r="D44">
+        <v>89.2478197145776</v>
+      </c>
+      <c r="E44">
+        <v>41.8</v>
+      </c>
+      <c r="F44">
+        <v>94.5</v>
+      </c>
+      <c r="G44">
+        <v>0.648</v>
+      </c>
+      <c r="H44">
+        <v>172.3</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K44">
+        <v>3.73</v>
+      </c>
+      <c r="L44">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M44">
+        <v>22.5666</v>
+      </c>
+      <c r="N44">
+        <v>-17.21326666666667</v>
+      </c>
+      <c r="O44">
+        <v>-3.442653333333334</v>
+      </c>
+      <c r="P44">
+        <v>-13.77061333333334</v>
+      </c>
+      <c r="Q44">
+        <v>-10.04061333333333</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1277218398937018</v>
+      </c>
+      <c r="T44">
+        <v>1.579049175710425</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.0474447487289475</v>
+      </c>
+      <c r="W44">
+        <v>0.2274701940035273</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.2372237436447374</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1716161486198286</v>
+      </c>
+      <c r="C45">
+        <v>-8.198110532489579</v>
+      </c>
+      <c r="D45">
+        <v>87.90388946751042</v>
+      </c>
+      <c r="E45">
+        <v>44.05</v>
+      </c>
+      <c r="F45">
+        <v>96.75</v>
+      </c>
+      <c r="G45">
+        <v>0.648</v>
+      </c>
+      <c r="H45">
+        <v>172.3</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K45">
+        <v>3.73</v>
+      </c>
+      <c r="L45">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M45">
+        <v>23.1039</v>
+      </c>
+      <c r="N45">
+        <v>-17.75056666666666</v>
+      </c>
+      <c r="O45">
+        <v>-3.550113333333333</v>
+      </c>
+      <c r="P45">
+        <v>-14.20045333333333</v>
+      </c>
+      <c r="Q45">
+        <v>-10.47045333333333</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1292818721725387</v>
+      </c>
+      <c r="T45">
+        <v>1.606751792828152</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.0463413824794371</v>
+      </c>
+      <c r="W45">
+        <v>0.2277336778639104</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.2317069123971855</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1736161486198285</v>
+      </c>
+      <c r="C46">
+        <v>-11.7521663205746</v>
+      </c>
+      <c r="D46">
+        <v>86.5998336794254</v>
+      </c>
+      <c r="E46">
+        <v>46.3</v>
+      </c>
+      <c r="F46">
+        <v>99</v>
+      </c>
+      <c r="G46">
+        <v>0.648</v>
+      </c>
+      <c r="H46">
+        <v>172.3</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K46">
+        <v>3.73</v>
+      </c>
+      <c r="L46">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M46">
+        <v>23.6412</v>
+      </c>
+      <c r="N46">
+        <v>-18.28786666666667</v>
+      </c>
+      <c r="O46">
+        <v>-3.657573333333334</v>
+      </c>
+      <c r="P46">
+        <v>-14.63029333333333</v>
+      </c>
+      <c r="Q46">
+        <v>-10.90029333333333</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1308976198899054</v>
+      </c>
+      <c r="T46">
+        <v>1.635443789128654</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.04528816924126807</v>
+      </c>
+      <c r="W46">
+        <v>0.2279851851851852</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.2264408462063404</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1756161486198285</v>
+      </c>
+      <c r="C47">
+        <v>-15.26809632303448</v>
+      </c>
+      <c r="D47">
+        <v>85.33390367696552</v>
+      </c>
+      <c r="E47">
+        <v>48.55</v>
+      </c>
+      <c r="F47">
+        <v>101.25</v>
+      </c>
+      <c r="G47">
+        <v>0.648</v>
+      </c>
+      <c r="H47">
+        <v>172.3</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K47">
+        <v>3.73</v>
+      </c>
+      <c r="L47">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M47">
+        <v>24.1785</v>
+      </c>
+      <c r="N47">
+        <v>-18.82516666666667</v>
+      </c>
+      <c r="O47">
+        <v>-3.765033333333334</v>
+      </c>
+      <c r="P47">
+        <v>-15.06013333333333</v>
+      </c>
+      <c r="Q47">
+        <v>-11.33013333333333</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1325721220697219</v>
+      </c>
+      <c r="T47">
+        <v>1.665179130749175</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.04428176548035101</v>
+      </c>
+      <c r="W47">
+        <v>0.2282255144032922</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.2214088274017549</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1776161486198286</v>
+      </c>
+      <c r="C48">
+        <v>-18.74754843686121</v>
+      </c>
+      <c r="D48">
+        <v>84.1044515631388</v>
+      </c>
+      <c r="E48">
+        <v>50.8</v>
+      </c>
+      <c r="F48">
+        <v>103.5</v>
+      </c>
+      <c r="G48">
+        <v>0.648</v>
+      </c>
+      <c r="H48">
+        <v>172.3</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K48">
+        <v>3.73</v>
+      </c>
+      <c r="L48">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M48">
+        <v>24.7158</v>
+      </c>
+      <c r="N48">
+        <v>-19.36246666666667</v>
+      </c>
+      <c r="O48">
+        <v>-3.872493333333334</v>
+      </c>
+      <c r="P48">
+        <v>-15.48997333333334</v>
+      </c>
+      <c r="Q48">
+        <v>-11.75997333333333</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1343086428487908</v>
+      </c>
+      <c r="T48">
+        <v>1.696015781318605</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.04331911840469119</v>
+      </c>
+      <c r="W48">
+        <v>0.2284553945249598</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.2165955920234559</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1796161486198286</v>
+      </c>
+      <c r="C49">
+        <v>-22.19207693927326</v>
+      </c>
+      <c r="D49">
+        <v>82.90992306072674</v>
+      </c>
+      <c r="E49">
+        <v>53.05</v>
+      </c>
+      <c r="F49">
+        <v>105.75</v>
+      </c>
+      <c r="G49">
+        <v>0.648</v>
+      </c>
+      <c r="H49">
+        <v>172.3</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K49">
+        <v>3.73</v>
+      </c>
+      <c r="L49">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M49">
+        <v>25.2531</v>
+      </c>
+      <c r="N49">
+        <v>-19.89976666666666</v>
+      </c>
+      <c r="O49">
+        <v>-3.979953333333333</v>
+      </c>
+      <c r="P49">
+        <v>-15.91981333333333</v>
+      </c>
+      <c r="Q49">
+        <v>-12.18981333333333</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1361106927138624</v>
+      </c>
+      <c r="T49">
+        <v>1.728016079079333</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.04239743503437862</v>
+      </c>
+      <c r="W49">
+        <v>0.2286754925137904</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.2119871751718931</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1816161486198286</v>
+      </c>
+      <c r="C50">
+        <v>-25.60314904298095</v>
+      </c>
+      <c r="D50">
+        <v>81.74885095701906</v>
+      </c>
+      <c r="E50">
+        <v>55.3</v>
+      </c>
+      <c r="F50">
+        <v>108</v>
+      </c>
+      <c r="G50">
+        <v>0.648</v>
+      </c>
+      <c r="H50">
+        <v>172.3</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K50">
+        <v>3.73</v>
+      </c>
+      <c r="L50">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M50">
+        <v>25.7904</v>
+      </c>
+      <c r="N50">
+        <v>-20.43706666666667</v>
+      </c>
+      <c r="O50">
+        <v>-4.087413333333333</v>
+      </c>
+      <c r="P50">
+        <v>-16.34965333333333</v>
+      </c>
+      <c r="Q50">
+        <v>-12.61965333333333</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.137982052189129</v>
+      </c>
+      <c r="T50">
+        <v>1.761247157523166</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.04151415513782906</v>
+      </c>
+      <c r="W50">
+        <v>0.2288864197530864</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.2075707756891454</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1836161486198286</v>
+      </c>
+      <c r="C51">
+        <v>-28.98215090825809</v>
+      </c>
+      <c r="D51">
+        <v>80.61984909174191</v>
+      </c>
+      <c r="E51">
+        <v>57.55</v>
+      </c>
+      <c r="F51">
+        <v>110.25</v>
+      </c>
+      <c r="G51">
+        <v>0.648</v>
+      </c>
+      <c r="H51">
+        <v>172.3</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K51">
+        <v>3.73</v>
+      </c>
+      <c r="L51">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M51">
+        <v>26.3277</v>
+      </c>
+      <c r="N51">
+        <v>-20.97436666666667</v>
+      </c>
+      <c r="O51">
+        <v>-4.194873333333334</v>
+      </c>
+      <c r="P51">
+        <v>-16.77949333333333</v>
+      </c>
+      <c r="Q51">
+        <v>-13.04949333333333</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1399267983104844</v>
+      </c>
+      <c r="T51">
+        <v>1.795781415513817</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.040666927481955</v>
+      </c>
+      <c r="W51">
+        <v>0.2290887377173092</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.203334637409775</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1856161486198286</v>
+      </c>
+      <c r="C52">
+        <v>-32.33039316361791</v>
+      </c>
+      <c r="D52">
+        <v>79.52160683638209</v>
+      </c>
+      <c r="E52">
+        <v>59.8</v>
+      </c>
+      <c r="F52">
+        <v>112.5</v>
+      </c>
+      <c r="G52">
+        <v>0.648</v>
+      </c>
+      <c r="H52">
+        <v>172.3</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K52">
+        <v>3.73</v>
+      </c>
+      <c r="L52">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M52">
+        <v>26.865</v>
+      </c>
+      <c r="N52">
+        <v>-21.51166666666667</v>
+      </c>
+      <c r="O52">
+        <v>-4.302333333333334</v>
+      </c>
+      <c r="P52">
+        <v>-17.20933333333334</v>
+      </c>
+      <c r="Q52">
+        <v>-13.47933333333334</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1419493342766941</v>
+      </c>
+      <c r="T52">
+        <v>1.831697043824093</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.0398535889323159</v>
+      </c>
+      <c r="W52">
+        <v>0.229282962962963</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.1992679446615794</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1876161486198286</v>
+      </c>
+      <c r="C53">
+        <v>-35.64911598132142</v>
+      </c>
+      <c r="D53">
+        <v>78.45288401867859</v>
+      </c>
+      <c r="E53">
+        <v>62.05</v>
+      </c>
+      <c r="F53">
+        <v>114.75</v>
+      </c>
+      <c r="G53">
+        <v>0.648</v>
+      </c>
+      <c r="H53">
+        <v>172.3</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K53">
+        <v>3.73</v>
+      </c>
+      <c r="L53">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M53">
+        <v>27.4023</v>
+      </c>
+      <c r="N53">
+        <v>-22.04896666666667</v>
+      </c>
+      <c r="O53">
+        <v>-4.409793333333333</v>
+      </c>
+      <c r="P53">
+        <v>-17.63917333333333</v>
+      </c>
+      <c r="Q53">
+        <v>-13.90917333333333</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1440544227313205</v>
+      </c>
+      <c r="T53">
+        <v>1.869078616147034</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.03907214601207442</v>
+      </c>
+      <c r="W53">
+        <v>0.2294695715323166</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.1953607300603721</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1896161486198285</v>
+      </c>
+      <c r="C54">
+        <v>-38.93949374904226</v>
+      </c>
+      <c r="D54">
+        <v>77.41250625095775</v>
+      </c>
+      <c r="E54">
+        <v>64.3</v>
+      </c>
+      <c r="F54">
+        <v>117</v>
+      </c>
+      <c r="G54">
+        <v>0.648</v>
+      </c>
+      <c r="H54">
+        <v>172.3</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K54">
+        <v>3.73</v>
+      </c>
+      <c r="L54">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M54">
+        <v>27.9396</v>
+      </c>
+      <c r="N54">
+        <v>-22.58626666666667</v>
+      </c>
+      <c r="O54">
+        <v>-4.517253333333334</v>
+      </c>
+      <c r="P54">
+        <v>-18.06901333333333</v>
+      </c>
+      <c r="Q54">
+        <v>-14.33901333333333</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1462472232048897</v>
+      </c>
+      <c r="T54">
+        <v>1.90801775398343</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.03832075858876529</v>
+      </c>
+      <c r="W54">
+        <v>0.2296490028490029</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.1916037929438265</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1916161486198285</v>
+      </c>
+      <c r="C55">
+        <v>-42.2026393746861</v>
+      </c>
+      <c r="D55">
+        <v>76.3993606253139</v>
+      </c>
+      <c r="E55">
+        <v>66.55</v>
+      </c>
+      <c r="F55">
+        <v>119.25</v>
+      </c>
+      <c r="G55">
+        <v>0.648</v>
+      </c>
+      <c r="H55">
+        <v>172.3</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K55">
+        <v>3.73</v>
+      </c>
+      <c r="L55">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M55">
+        <v>28.4769</v>
+      </c>
+      <c r="N55">
+        <v>-23.12356666666667</v>
+      </c>
+      <c r="O55">
+        <v>-4.624713333333334</v>
+      </c>
+      <c r="P55">
+        <v>-18.49885333333334</v>
+      </c>
+      <c r="Q55">
+        <v>-14.76885333333334</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1485333343369086</v>
+      </c>
+      <c r="T55">
+        <v>1.94861387640861</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.03759772540784519</v>
+      </c>
+      <c r="W55">
+        <v>0.2298216631726066</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.1879886270392259</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1936161486198286</v>
+      </c>
+      <c r="C56">
+        <v>-45.43960825753726</v>
+      </c>
+      <c r="D56">
+        <v>75.41239174246276</v>
+      </c>
+      <c r="E56">
+        <v>68.80000000000001</v>
+      </c>
+      <c r="F56">
+        <v>121.5</v>
+      </c>
+      <c r="G56">
+        <v>0.648</v>
+      </c>
+      <c r="H56">
+        <v>172.3</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K56">
+        <v>3.73</v>
+      </c>
+      <c r="L56">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M56">
+        <v>29.01420000000001</v>
+      </c>
+      <c r="N56">
+        <v>-23.66086666666667</v>
+      </c>
+      <c r="O56">
+        <v>-4.732173333333335</v>
+      </c>
+      <c r="P56">
+        <v>-18.92869333333334</v>
+      </c>
+      <c r="Q56">
+        <v>-15.19869333333333</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1509188416051023</v>
+      </c>
+      <c r="T56">
+        <v>1.990975047634884</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.03690147123362583</v>
+      </c>
+      <c r="W56">
+        <v>0.2299879286694101</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.1845073561681292</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1956161486198285</v>
+      </c>
+      <c r="C57">
+        <v>-48.65140195552286</v>
+      </c>
+      <c r="D57">
+        <v>74.45059804447716</v>
+      </c>
+      <c r="E57">
+        <v>71.05000000000001</v>
+      </c>
+      <c r="F57">
+        <v>123.75</v>
+      </c>
+      <c r="G57">
+        <v>0.648</v>
+      </c>
+      <c r="H57">
+        <v>172.3</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K57">
+        <v>3.73</v>
+      </c>
+      <c r="L57">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M57">
+        <v>29.5515</v>
+      </c>
+      <c r="N57">
+        <v>-24.19816666666667</v>
+      </c>
+      <c r="O57">
+        <v>-4.839633333333335</v>
+      </c>
+      <c r="P57">
+        <v>-19.35853333333334</v>
+      </c>
+      <c r="Q57">
+        <v>-15.62853333333334</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.153410371418549</v>
+      </c>
+      <c r="T57">
+        <v>2.035218937582326</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.03623053539301446</v>
+      </c>
+      <c r="W57">
+        <v>0.2301481481481482</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.1811526769650722</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1976161486198286</v>
+      </c>
+      <c r="C58">
+        <v>-51.83897157538181</v>
+      </c>
+      <c r="D58">
+        <v>73.51302842461821</v>
+      </c>
+      <c r="E58">
+        <v>73.30000000000001</v>
+      </c>
+      <c r="F58">
+        <v>126</v>
+      </c>
+      <c r="G58">
+        <v>0.648</v>
+      </c>
+      <c r="H58">
+        <v>172.3</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K58">
+        <v>3.73</v>
+      </c>
+      <c r="L58">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M58">
+        <v>30.08880000000001</v>
+      </c>
+      <c r="N58">
+        <v>-24.73546666666667</v>
+      </c>
+      <c r="O58">
+        <v>-4.947093333333335</v>
+      </c>
+      <c r="P58">
+        <v>-19.78837333333334</v>
+      </c>
+      <c r="Q58">
+        <v>-16.05837333333334</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1560151525871524</v>
+      </c>
+      <c r="T58">
+        <v>2.081473913436469</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.03558356154671062</v>
+      </c>
+      <c r="W58">
+        <v>0.2303026455026455</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.177917807733553</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1996161486198286</v>
+      </c>
+      <c r="C59">
+        <v>-55.0032209098613</v>
+      </c>
+      <c r="D59">
+        <v>72.59877909013871</v>
+      </c>
+      <c r="E59">
+        <v>75.55</v>
+      </c>
+      <c r="F59">
+        <v>128.25</v>
+      </c>
+      <c r="G59">
+        <v>0.648</v>
+      </c>
+      <c r="H59">
+        <v>172.3</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K59">
+        <v>3.73</v>
+      </c>
+      <c r="L59">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M59">
+        <v>30.6261</v>
+      </c>
+      <c r="N59">
+        <v>-25.27276666666667</v>
+      </c>
+      <c r="O59">
+        <v>-5.054553333333335</v>
+      </c>
+      <c r="P59">
+        <v>-20.21821333333333</v>
+      </c>
+      <c r="Q59">
+        <v>-16.48821333333333</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.158741086368249</v>
+      </c>
+      <c r="T59">
+        <v>2.129880283516387</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.03495928853711921</v>
+      </c>
+      <c r="W59">
+        <v>0.230451721897336</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.174796442685596</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2016161486198285</v>
+      </c>
+      <c r="C60">
+        <v>-58.14500934369354</v>
+      </c>
+      <c r="D60">
+        <v>71.70699065630646</v>
+      </c>
+      <c r="E60">
+        <v>77.8</v>
+      </c>
+      <c r="F60">
+        <v>130.5</v>
+      </c>
+      <c r="G60">
+        <v>0.648</v>
+      </c>
+      <c r="H60">
+        <v>172.3</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K60">
+        <v>3.73</v>
+      </c>
+      <c r="L60">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M60">
+        <v>31.1634</v>
+      </c>
+      <c r="N60">
+        <v>-25.81006666666667</v>
+      </c>
+      <c r="O60">
+        <v>-5.162013333333334</v>
+      </c>
+      <c r="P60">
+        <v>-20.64805333333334</v>
+      </c>
+      <c r="Q60">
+        <v>-16.91805333333334</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1615968265198739</v>
+      </c>
+      <c r="T60">
+        <v>2.180591718838206</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.03435654218303095</v>
+      </c>
+      <c r="W60">
+        <v>0.2305956577266922</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.1717827109151546</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2036161486198285</v>
+      </c>
+      <c r="C61">
+        <v>-61.26515454799279</v>
+      </c>
+      <c r="D61">
+        <v>70.83684545200721</v>
+      </c>
+      <c r="E61">
+        <v>80.05</v>
+      </c>
+      <c r="F61">
+        <v>132.75</v>
+      </c>
+      <c r="G61">
+        <v>0.648</v>
+      </c>
+      <c r="H61">
+        <v>172.3</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K61">
+        <v>3.73</v>
+      </c>
+      <c r="L61">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M61">
+        <v>31.7007</v>
+      </c>
+      <c r="N61">
+        <v>-26.34736666666667</v>
+      </c>
+      <c r="O61">
+        <v>-5.269473333333334</v>
+      </c>
+      <c r="P61">
+        <v>-21.07789333333333</v>
+      </c>
+      <c r="Q61">
+        <v>-17.34789333333333</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1645918710691391</v>
+      </c>
+      <c r="T61">
+        <v>2.233776882712308</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.03377422790874229</v>
+      </c>
+      <c r="W61">
+        <v>0.2307347143753924</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.1688711395437115</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2056161486198285</v>
+      </c>
+      <c r="C62">
+        <v>-64.36443498082957</v>
+      </c>
+      <c r="D62">
+        <v>69.98756501917043</v>
+      </c>
+      <c r="E62">
+        <v>82.3</v>
+      </c>
+      <c r="F62">
+        <v>135</v>
+      </c>
+      <c r="G62">
+        <v>0.648</v>
+      </c>
+      <c r="H62">
+        <v>172.3</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K62">
+        <v>3.73</v>
+      </c>
+      <c r="L62">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M62">
+        <v>32.238</v>
+      </c>
+      <c r="N62">
+        <v>-26.88466666666667</v>
+      </c>
+      <c r="O62">
+        <v>-5.376933333333334</v>
+      </c>
+      <c r="P62">
+        <v>-21.50773333333333</v>
+      </c>
+      <c r="Q62">
+        <v>-17.77773333333333</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1677366678458676</v>
+      </c>
+      <c r="T62">
+        <v>2.289621304780116</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.03321132411026325</v>
+      </c>
+      <c r="W62">
+        <v>0.2308691358024691</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.1660566205513162</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2076161486198286</v>
+      </c>
+      <c r="C63">
+        <v>-67.44359221005629</v>
+      </c>
+      <c r="D63">
+        <v>69.15840778994371</v>
+      </c>
+      <c r="E63">
+        <v>84.55</v>
+      </c>
+      <c r="F63">
+        <v>137.25</v>
+      </c>
+      <c r="G63">
+        <v>0.648</v>
+      </c>
+      <c r="H63">
+        <v>172.3</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K63">
+        <v>3.73</v>
+      </c>
+      <c r="L63">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M63">
+        <v>32.7753</v>
+      </c>
+      <c r="N63">
+        <v>-27.42196666666667</v>
+      </c>
+      <c r="O63">
+        <v>-5.484393333333334</v>
+      </c>
+      <c r="P63">
+        <v>-21.93757333333334</v>
+      </c>
+      <c r="Q63">
+        <v>-18.20757333333334</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.171042736252172</v>
+      </c>
+      <c r="T63">
+        <v>2.348329543364222</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.03266687617402943</v>
+      </c>
+      <c r="W63">
+        <v>0.2309991499696418</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.1633343808701471</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2096161486198285</v>
+      </c>
+      <c r="C64">
+        <v>-70.50333307295168</v>
+      </c>
+      <c r="D64">
+        <v>68.34866692704833</v>
+      </c>
+      <c r="E64">
+        <v>86.8</v>
+      </c>
+      <c r="F64">
+        <v>139.5</v>
+      </c>
+      <c r="G64">
+        <v>0.648</v>
+      </c>
+      <c r="H64">
+        <v>172.3</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K64">
+        <v>3.73</v>
+      </c>
+      <c r="L64">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M64">
+        <v>33.3126</v>
+      </c>
+      <c r="N64">
+        <v>-27.95926666666667</v>
+      </c>
+      <c r="O64">
+        <v>-5.591853333333335</v>
+      </c>
+      <c r="P64">
+        <v>-22.36741333333334</v>
+      </c>
+      <c r="Q64">
+        <v>-18.63741333333334</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.174522808258808</v>
+      </c>
+      <c r="T64">
+        <v>2.410127689242227</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.03213999107444831</v>
+      </c>
+      <c r="W64">
+        <v>0.2311249701314217</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.1606999553722415</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2116161486198286</v>
+      </c>
+      <c r="C65">
+        <v>-73.5443316859043</v>
+      </c>
+      <c r="D65">
+        <v>67.55766831409571</v>
+      </c>
+      <c r="E65">
+        <v>89.05</v>
+      </c>
+      <c r="F65">
+        <v>141.75</v>
+      </c>
+      <c r="G65">
+        <v>0.648</v>
+      </c>
+      <c r="H65">
+        <v>172.3</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K65">
+        <v>3.73</v>
+      </c>
+      <c r="L65">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M65">
+        <v>33.84990000000001</v>
+      </c>
+      <c r="N65">
+        <v>-28.49656666666667</v>
+      </c>
+      <c r="O65">
+        <v>-5.699313333333335</v>
+      </c>
+      <c r="P65">
+        <v>-22.79725333333334</v>
+      </c>
+      <c r="Q65">
+        <v>-19.06725333333334</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1781909922658029</v>
+      </c>
+      <c r="T65">
+        <v>2.475266275437964</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.031629832485965</v>
+      </c>
+      <c r="W65">
+        <v>0.2312467960023516</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.1581491624298249</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2136161486198286</v>
+      </c>
+      <c r="C66">
+        <v>-76.56723131614397</v>
+      </c>
+      <c r="D66">
+        <v>66.78476868385603</v>
+      </c>
+      <c r="E66">
+        <v>91.3</v>
+      </c>
+      <c r="F66">
+        <v>144</v>
+      </c>
+      <c r="G66">
+        <v>0.648</v>
+      </c>
+      <c r="H66">
+        <v>172.3</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K66">
+        <v>3.73</v>
+      </c>
+      <c r="L66">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M66">
+        <v>34.3872</v>
+      </c>
+      <c r="N66">
+        <v>-29.03386666666667</v>
+      </c>
+      <c r="O66">
+        <v>-5.806773333333334</v>
+      </c>
+      <c r="P66">
+        <v>-23.22709333333334</v>
+      </c>
+      <c r="Q66">
+        <v>-19.49709333333334</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1820629642731863</v>
+      </c>
+      <c r="T66">
+        <v>2.544023671977907</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.0311356163533718</v>
+      </c>
+      <c r="W66">
+        <v>0.2313648148148148</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.1556780817668589</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2156161486198286</v>
+      </c>
+      <c r="C67">
+        <v>-79.57264612644447</v>
+      </c>
+      <c r="D67">
+        <v>66.02935387355554</v>
+      </c>
+      <c r="E67">
+        <v>93.55</v>
+      </c>
+      <c r="F67">
+        <v>146.25</v>
+      </c>
+      <c r="G67">
+        <v>0.648</v>
+      </c>
+      <c r="H67">
+        <v>172.3</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K67">
+        <v>3.73</v>
+      </c>
+      <c r="L67">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M67">
+        <v>34.9245</v>
+      </c>
+      <c r="N67">
+        <v>-29.57116666666667</v>
+      </c>
+      <c r="O67">
+        <v>-5.914233333333335</v>
+      </c>
+      <c r="P67">
+        <v>-23.65693333333333</v>
+      </c>
+      <c r="Q67">
+        <v>-19.92693333333333</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1861561918238487</v>
+      </c>
+      <c r="T67">
+        <v>2.616710062605847</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.03065660687101223</v>
+      </c>
+      <c r="W67">
+        <v>0.2314792022792023</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.1532830343550611</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2176161486198286</v>
+      </c>
+      <c r="C68">
+        <v>-82.56116280274239</v>
+      </c>
+      <c r="D68">
+        <v>65.29083719725762</v>
+      </c>
+      <c r="E68">
+        <v>95.8</v>
+      </c>
+      <c r="F68">
+        <v>148.5</v>
+      </c>
+      <c r="G68">
+        <v>0.648</v>
+      </c>
+      <c r="H68">
+        <v>172.3</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K68">
+        <v>3.73</v>
+      </c>
+      <c r="L68">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M68">
+        <v>35.4618</v>
+      </c>
+      <c r="N68">
+        <v>-30.10846666666667</v>
+      </c>
+      <c r="O68">
+        <v>-6.021693333333335</v>
+      </c>
+      <c r="P68">
+        <v>-24.08677333333334</v>
+      </c>
+      <c r="Q68">
+        <v>-20.35677333333334</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1904901974657267</v>
+      </c>
+      <c r="T68">
+        <v>2.693672123270725</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.03019211282751204</v>
+      </c>
+      <c r="W68">
+        <v>0.2315901234567901</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.1509605641375602</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2196161486198286</v>
+      </c>
+      <c r="C69">
+        <v>-85.53334207373808</v>
+      </c>
+      <c r="D69">
+        <v>64.56865792626192</v>
+      </c>
+      <c r="E69">
+        <v>98.05</v>
+      </c>
+      <c r="F69">
+        <v>150.75</v>
+      </c>
+      <c r="G69">
+        <v>0.648</v>
+      </c>
+      <c r="H69">
+        <v>172.3</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K69">
+        <v>3.73</v>
+      </c>
+      <c r="L69">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M69">
+        <v>35.9991</v>
+      </c>
+      <c r="N69">
+        <v>-30.64576666666667</v>
+      </c>
+      <c r="O69">
+        <v>-6.129153333333334</v>
+      </c>
+      <c r="P69">
+        <v>-24.51661333333333</v>
+      </c>
+      <c r="Q69">
+        <v>-20.78661333333333</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1950868701162032</v>
+      </c>
+      <c r="T69">
+        <v>2.775298551248626</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.02974148427784769</v>
+      </c>
+      <c r="W69">
+        <v>0.23169773355445</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.1487074213892384</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2216161486198286</v>
+      </c>
+      <c r="C70">
+        <v>-88.48972013075026</v>
+      </c>
+      <c r="D70">
+        <v>63.86227986924975</v>
+      </c>
+      <c r="E70">
+        <v>100.3</v>
+      </c>
+      <c r="F70">
+        <v>153</v>
+      </c>
+      <c r="G70">
+        <v>0.648</v>
+      </c>
+      <c r="H70">
+        <v>172.3</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K70">
+        <v>3.73</v>
+      </c>
+      <c r="L70">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M70">
+        <v>36.5364</v>
+      </c>
+      <c r="N70">
+        <v>-31.18306666666667</v>
+      </c>
+      <c r="O70">
+        <v>-6.236613333333334</v>
+      </c>
+      <c r="P70">
+        <v>-24.94645333333333</v>
+      </c>
+      <c r="Q70">
+        <v>-21.21645333333333</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1999708348073346</v>
+      </c>
+      <c r="T70">
+        <v>2.862026630975146</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.02930410950905581</v>
+      </c>
+      <c r="W70">
+        <v>0.2318021786492375</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.146520547545279</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2236161486198285</v>
+      </c>
+      <c r="C71">
+        <v>-91.43080995538041</v>
+      </c>
+      <c r="D71">
+        <v>63.17119004461959</v>
+      </c>
+      <c r="E71">
+        <v>102.55</v>
+      </c>
+      <c r="F71">
+        <v>155.25</v>
+      </c>
+      <c r="G71">
+        <v>0.648</v>
+      </c>
+      <c r="H71">
+        <v>172.3</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K71">
+        <v>3.73</v>
+      </c>
+      <c r="L71">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M71">
+        <v>37.0737</v>
+      </c>
+      <c r="N71">
+        <v>-31.72036666666667</v>
+      </c>
+      <c r="O71">
+        <v>-6.344073333333334</v>
+      </c>
+      <c r="P71">
+        <v>-25.37629333333334</v>
+      </c>
+      <c r="Q71">
+        <v>-21.64629333333334</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.205169893994668</v>
+      </c>
+      <c r="T71">
+        <v>2.954350070684021</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.02887941226979413</v>
+      </c>
+      <c r="W71">
+        <v>0.2319035963499732</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.1443970613489706</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2256161486198286</v>
+      </c>
+      <c r="C72">
+        <v>-94.35710256189567</v>
+      </c>
+      <c r="D72">
+        <v>62.49489743810435</v>
+      </c>
+      <c r="E72">
+        <v>104.8</v>
+      </c>
+      <c r="F72">
+        <v>157.5</v>
+      </c>
+      <c r="G72">
+        <v>0.648</v>
+      </c>
+      <c r="H72">
+        <v>172.3</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K72">
+        <v>3.73</v>
+      </c>
+      <c r="L72">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M72">
+        <v>37.61100000000001</v>
+      </c>
+      <c r="N72">
+        <v>-32.25766666666668</v>
+      </c>
+      <c r="O72">
+        <v>-6.451533333333336</v>
+      </c>
+      <c r="P72">
+        <v>-25.80613333333334</v>
+      </c>
+      <c r="Q72">
+        <v>-22.07613333333334</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2107155571278236</v>
+      </c>
+      <c r="T72">
+        <v>3.052828406373489</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.02846684923736849</v>
+      </c>
+      <c r="W72">
+        <v>0.2320021164021164</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.1423342461868424</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2276161486198285</v>
+      </c>
+      <c r="C73">
+        <v>-97.26906816065312</v>
+      </c>
+      <c r="D73">
+        <v>61.83293183934688</v>
+      </c>
+      <c r="E73">
+        <v>107.05</v>
+      </c>
+      <c r="F73">
+        <v>159.75</v>
+      </c>
+      <c r="G73">
+        <v>0.648</v>
+      </c>
+      <c r="H73">
+        <v>172.3</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K73">
+        <v>3.73</v>
+      </c>
+      <c r="L73">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M73">
+        <v>38.1483</v>
+      </c>
+      <c r="N73">
+        <v>-32.79496666666667</v>
+      </c>
+      <c r="O73">
+        <v>-6.558993333333333</v>
+      </c>
+      <c r="P73">
+        <v>-26.23597333333333</v>
+      </c>
+      <c r="Q73">
+        <v>-22.50597333333333</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2166436797874036</v>
+      </c>
+      <c r="T73">
+        <v>3.15809835142085</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.02806590769881402</v>
+      </c>
+      <c r="W73">
+        <v>0.2320978612415232</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.14032953849407</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2296161486198285</v>
+      </c>
+      <c r="C74">
+        <v>-100.1671572483596</v>
+      </c>
+      <c r="D74">
+        <v>61.18484275164037</v>
+      </c>
+      <c r="E74">
+        <v>109.3</v>
+      </c>
+      <c r="F74">
+        <v>162</v>
+      </c>
+      <c r="G74">
+        <v>0.648</v>
+      </c>
+      <c r="H74">
+        <v>172.3</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K74">
+        <v>3.73</v>
+      </c>
+      <c r="L74">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M74">
+        <v>38.6856</v>
+      </c>
+      <c r="N74">
+        <v>-33.33226666666667</v>
+      </c>
+      <c r="O74">
+        <v>-6.666453333333334</v>
+      </c>
+      <c r="P74">
+        <v>-26.66581333333334</v>
+      </c>
+      <c r="Q74">
+        <v>-22.93581333333334</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2229952397798109</v>
+      </c>
+      <c r="T74">
+        <v>3.270887578257308</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.02767610342521938</v>
+      </c>
+      <c r="W74">
+        <v>0.2321909465020576</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.1383805171260968</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2316161486198285</v>
+      </c>
+      <c r="C75">
+        <v>-103.051801630478</v>
+      </c>
+      <c r="D75">
+        <v>60.55019836952197</v>
+      </c>
+      <c r="E75">
+        <v>111.55</v>
+      </c>
+      <c r="F75">
+        <v>164.25</v>
+      </c>
+      <c r="G75">
+        <v>0.648</v>
+      </c>
+      <c r="H75">
+        <v>172.3</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K75">
+        <v>3.73</v>
+      </c>
+      <c r="L75">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M75">
+        <v>39.2229</v>
+      </c>
+      <c r="N75">
+        <v>-33.86956666666667</v>
+      </c>
+      <c r="O75">
+        <v>-6.773913333333335</v>
+      </c>
+      <c r="P75">
+        <v>-27.09565333333334</v>
+      </c>
+      <c r="Q75">
+        <v>-23.36565333333334</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2298172856975817</v>
+      </c>
+      <c r="T75">
+        <v>3.392031562637209</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.02729697872076432</v>
+      </c>
+      <c r="W75">
+        <v>0.2322814814814815</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.1364848936038215</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2336161486198285</v>
+      </c>
+      <c r="C76">
+        <v>-105.9234153806572</v>
+      </c>
+      <c r="D76">
+        <v>59.92858461934275</v>
+      </c>
+      <c r="E76">
+        <v>113.8</v>
+      </c>
+      <c r="F76">
+        <v>166.5</v>
+      </c>
+      <c r="G76">
+        <v>0.648</v>
+      </c>
+      <c r="H76">
+        <v>172.3</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K76">
+        <v>3.73</v>
+      </c>
+      <c r="L76">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M76">
+        <v>39.7602</v>
+      </c>
+      <c r="N76">
+        <v>-34.40686666666667</v>
+      </c>
+      <c r="O76">
+        <v>-6.881373333333335</v>
+      </c>
+      <c r="P76">
+        <v>-27.52549333333334</v>
+      </c>
+      <c r="Q76">
+        <v>-23.79549333333334</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2371641043782579</v>
+      </c>
+      <c r="T76">
+        <v>3.522494315046332</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.02692810062994318</v>
+      </c>
+      <c r="W76">
+        <v>0.2323695695695696</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.1346405031497159</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2356161486198285</v>
+      </c>
+      <c r="C77">
+        <v>-108.7823957416651</v>
+      </c>
+      <c r="D77">
+        <v>59.31960425833486</v>
+      </c>
+      <c r="E77">
+        <v>116.05</v>
+      </c>
+      <c r="F77">
+        <v>168.75</v>
+      </c>
+      <c r="G77">
+        <v>0.648</v>
+      </c>
+      <c r="H77">
+        <v>172.3</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K77">
+        <v>3.73</v>
+      </c>
+      <c r="L77">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M77">
+        <v>40.2975</v>
+      </c>
+      <c r="N77">
+        <v>-34.94416666666667</v>
+      </c>
+      <c r="O77">
+        <v>-6.988833333333334</v>
+      </c>
+      <c r="P77">
+        <v>-27.95533333333334</v>
+      </c>
+      <c r="Q77">
+        <v>-24.22533333333334</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2450986685533882</v>
+      </c>
+      <c r="T77">
+        <v>3.663394087648186</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.0265690592882106</v>
+      </c>
+      <c r="W77">
+        <v>0.2324553086419753</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.1328452964410529</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2376161486198285</v>
+      </c>
+      <c r="C78">
+        <v>-111.6291239719435</v>
+      </c>
+      <c r="D78">
+        <v>58.72287602805651</v>
+      </c>
+      <c r="E78">
+        <v>118.3</v>
+      </c>
+      <c r="F78">
+        <v>171</v>
+      </c>
+      <c r="G78">
+        <v>0.648</v>
+      </c>
+      <c r="H78">
+        <v>172.3</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K78">
+        <v>3.73</v>
+      </c>
+      <c r="L78">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M78">
+        <v>40.8348</v>
+      </c>
+      <c r="N78">
+        <v>-35.48146666666667</v>
+      </c>
+      <c r="O78">
+        <v>-7.096293333333334</v>
+      </c>
+      <c r="P78">
+        <v>-28.38517333333333</v>
+      </c>
+      <c r="Q78">
+        <v>-24.65517333333333</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2536944464097795</v>
+      </c>
+      <c r="T78">
+        <v>3.81603550796686</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.02621946640283941</v>
+      </c>
+      <c r="W78">
+        <v>0.232538791423002</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.131097332014197</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2396161486198286</v>
+      </c>
+      <c r="C79">
+        <v>-114.4639661415763</v>
+      </c>
+      <c r="D79">
+        <v>58.13803385842374</v>
+      </c>
+      <c r="E79">
+        <v>120.55</v>
+      </c>
+      <c r="F79">
+        <v>173.25</v>
+      </c>
+      <c r="G79">
+        <v>0.648</v>
+      </c>
+      <c r="H79">
+        <v>172.3</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K79">
+        <v>3.73</v>
+      </c>
+      <c r="L79">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M79">
+        <v>41.3721</v>
+      </c>
+      <c r="N79">
+        <v>-36.01876666666667</v>
+      </c>
+      <c r="O79">
+        <v>-7.203753333333335</v>
+      </c>
+      <c r="P79">
+        <v>-28.81501333333334</v>
+      </c>
+      <c r="Q79">
+        <v>-25.08501333333334</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2630376832102046</v>
+      </c>
+      <c r="T79">
+        <v>3.981950095269768</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.02587895385215318</v>
+      </c>
+      <c r="W79">
+        <v>0.2326201058201058</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.1293947692607659</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2416161486198286</v>
+      </c>
+      <c r="C80">
+        <v>-117.2872738811626</v>
+      </c>
+      <c r="D80">
+        <v>57.56472611883737</v>
+      </c>
+      <c r="E80">
+        <v>122.8</v>
+      </c>
+      <c r="F80">
+        <v>175.5</v>
+      </c>
+      <c r="G80">
+        <v>0.648</v>
+      </c>
+      <c r="H80">
+        <v>172.3</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K80">
+        <v>3.73</v>
+      </c>
+      <c r="L80">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M80">
+        <v>41.90940000000001</v>
+      </c>
+      <c r="N80">
+        <v>-36.55606666666667</v>
+      </c>
+      <c r="O80">
+        <v>-7.311213333333335</v>
+      </c>
+      <c r="P80">
+        <v>-29.24485333333334</v>
+      </c>
+      <c r="Q80">
+        <v>-25.51485333333334</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2732303051743048</v>
+      </c>
+      <c r="T80">
+        <v>4.162947826872939</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.02554717239251019</v>
+      </c>
+      <c r="W80">
+        <v>0.2326993352326686</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.1277358619625509</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2436161486198286</v>
+      </c>
+      <c r="C81">
+        <v>-120.0993850868145</v>
+      </c>
+      <c r="D81">
+        <v>57.00261491318546</v>
+      </c>
+      <c r="E81">
+        <v>125.05</v>
+      </c>
+      <c r="F81">
+        <v>177.75</v>
+      </c>
+      <c r="G81">
+        <v>0.648</v>
+      </c>
+      <c r="H81">
+        <v>172.3</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K81">
+        <v>3.73</v>
+      </c>
+      <c r="L81">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M81">
+        <v>42.4467</v>
+      </c>
+      <c r="N81">
+        <v>-37.09336666666667</v>
+      </c>
+      <c r="O81">
+        <v>-7.418673333333334</v>
+      </c>
+      <c r="P81">
+        <v>-29.67469333333333</v>
+      </c>
+      <c r="Q81">
+        <v>-25.94469333333333</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2843936530397479</v>
+      </c>
+      <c r="T81">
+        <v>4.361183437676412</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.02522379046349107</v>
+      </c>
+      <c r="W81">
+        <v>0.2327765588373183</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.1261189523174553</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2456161486198286</v>
+      </c>
+      <c r="C82">
+        <v>-122.9006245842482</v>
+      </c>
+      <c r="D82">
+        <v>56.45137541575174</v>
+      </c>
+      <c r="E82">
+        <v>127.3</v>
+      </c>
+      <c r="F82">
+        <v>180</v>
+      </c>
+      <c r="G82">
+        <v>0.648</v>
+      </c>
+      <c r="H82">
+        <v>172.3</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K82">
+        <v>3.73</v>
+      </c>
+      <c r="L82">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M82">
+        <v>42.984</v>
+      </c>
+      <c r="N82">
+        <v>-37.63066666666667</v>
+      </c>
+      <c r="O82">
+        <v>-7.526133333333334</v>
+      </c>
+      <c r="P82">
+        <v>-30.10453333333334</v>
+      </c>
+      <c r="Q82">
+        <v>-26.37453333333334</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2966733356917353</v>
+      </c>
+      <c r="T82">
+        <v>4.579242609560233</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.02490849308269744</v>
+      </c>
+      <c r="W82">
+        <v>0.2328518518518518</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.1245424654134871</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2476161486198285</v>
+      </c>
+      <c r="C83">
+        <v>-125.6913047547127</v>
+      </c>
+      <c r="D83">
+        <v>55.91069524528728</v>
+      </c>
+      <c r="E83">
+        <v>129.55</v>
+      </c>
+      <c r="F83">
+        <v>182.25</v>
+      </c>
+      <c r="G83">
+        <v>0.648</v>
+      </c>
+      <c r="H83">
+        <v>172.3</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K83">
+        <v>3.73</v>
+      </c>
+      <c r="L83">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M83">
+        <v>43.5213</v>
+      </c>
+      <c r="N83">
+        <v>-38.16796666666667</v>
+      </c>
+      <c r="O83">
+        <v>-7.633593333333335</v>
+      </c>
+      <c r="P83">
+        <v>-30.53437333333334</v>
+      </c>
+      <c r="Q83">
+        <v>-26.80437333333334</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3102456165176161</v>
+      </c>
+      <c r="T83">
+        <v>4.820255378484456</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.02460098082241722</v>
+      </c>
+      <c r="W83">
+        <v>0.2329252857796068</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.1230049041120861</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2496161486198286</v>
+      </c>
+      <c r="C84">
+        <v>-128.4717261252892</v>
+      </c>
+      <c r="D84">
+        <v>55.38027387471082</v>
+      </c>
+      <c r="E84">
+        <v>131.8</v>
+      </c>
+      <c r="F84">
+        <v>184.5</v>
+      </c>
+      <c r="G84">
+        <v>0.648</v>
+      </c>
+      <c r="H84">
+        <v>172.3</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K84">
+        <v>3.73</v>
+      </c>
+      <c r="L84">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M84">
+        <v>44.05860000000001</v>
+      </c>
+      <c r="N84">
+        <v>-38.70526666666667</v>
+      </c>
+      <c r="O84">
+        <v>-7.741053333333335</v>
+      </c>
+      <c r="P84">
+        <v>-30.96421333333334</v>
+      </c>
+      <c r="Q84">
+        <v>-27.23421333333334</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3253259285463726</v>
+      </c>
+      <c r="T84">
+        <v>5.088047343955814</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.02430096886116823</v>
+      </c>
+      <c r="W84">
+        <v>0.232996928635953</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.1215048443058411</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2516161486198286</v>
+      </c>
+      <c r="C85">
+        <v>-131.2421779259055</v>
+      </c>
+      <c r="D85">
+        <v>54.85982207409452</v>
+      </c>
+      <c r="E85">
+        <v>134.05</v>
+      </c>
+      <c r="F85">
+        <v>186.75</v>
+      </c>
+      <c r="G85">
+        <v>0.648</v>
+      </c>
+      <c r="H85">
+        <v>172.3</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K85">
+        <v>3.73</v>
+      </c>
+      <c r="L85">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M85">
+        <v>44.59590000000001</v>
+      </c>
+      <c r="N85">
+        <v>-39.24256666666668</v>
+      </c>
+      <c r="O85">
+        <v>-7.848513333333336</v>
+      </c>
+      <c r="P85">
+        <v>-31.39405333333334</v>
+      </c>
+      <c r="Q85">
+        <v>-27.66405333333334</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3421803949314534</v>
+      </c>
+      <c r="T85">
+        <v>5.387344246541452</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.02400818610380476</v>
+      </c>
+      <c r="W85">
+        <v>0.2330668451584114</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.1200409305190238</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2536161486198286</v>
+      </c>
+      <c r="C86">
+        <v>-134.0029386152351</v>
+      </c>
+      <c r="D86">
+        <v>54.34906138476492</v>
+      </c>
+      <c r="E86">
+        <v>136.3</v>
+      </c>
+      <c r="F86">
+        <v>189</v>
+      </c>
+      <c r="G86">
+        <v>0.648</v>
+      </c>
+      <c r="H86">
+        <v>172.3</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K86">
+        <v>3.73</v>
+      </c>
+      <c r="L86">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M86">
+        <v>45.1332</v>
+      </c>
+      <c r="N86">
+        <v>-39.77986666666667</v>
+      </c>
+      <c r="O86">
+        <v>-7.955973333333334</v>
+      </c>
+      <c r="P86">
+        <v>-31.82389333333334</v>
+      </c>
+      <c r="Q86">
+        <v>-28.09389333333334</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.361141669614669</v>
+      </c>
+      <c r="T86">
+        <v>5.72405326195029</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.02372237436447375</v>
+      </c>
+      <c r="W86">
+        <v>0.2331350970017637</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.1186118718223688</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2556161486198285</v>
+      </c>
+      <c r="C87">
+        <v>-136.7542763774887</v>
+      </c>
+      <c r="D87">
+        <v>53.84772362251125</v>
+      </c>
+      <c r="E87">
+        <v>138.55</v>
+      </c>
+      <c r="F87">
+        <v>191.25</v>
+      </c>
+      <c r="G87">
+        <v>0.648</v>
+      </c>
+      <c r="H87">
+        <v>172.3</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K87">
+        <v>3.73</v>
+      </c>
+      <c r="L87">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M87">
+        <v>45.6705</v>
+      </c>
+      <c r="N87">
+        <v>-40.31716666666667</v>
+      </c>
+      <c r="O87">
+        <v>-8.063433333333334</v>
+      </c>
+      <c r="P87">
+        <v>-32.25373333333334</v>
+      </c>
+      <c r="Q87">
+        <v>-28.52373333333334</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.382631114255647</v>
+      </c>
+      <c r="T87">
+        <v>6.105656812746975</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.02344328760724465</v>
+      </c>
+      <c r="W87">
+        <v>0.23320174291939</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.1172164380362232</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2576161486198285</v>
+      </c>
+      <c r="C88">
+        <v>-139.4964495919627</v>
+      </c>
+      <c r="D88">
+        <v>53.35555040803734</v>
+      </c>
+      <c r="E88">
+        <v>140.8</v>
+      </c>
+      <c r="F88">
+        <v>193.5</v>
+      </c>
+      <c r="G88">
+        <v>0.648</v>
+      </c>
+      <c r="H88">
+        <v>172.3</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K88">
+        <v>3.73</v>
+      </c>
+      <c r="L88">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M88">
+        <v>46.2078</v>
+      </c>
+      <c r="N88">
+        <v>-40.85446666666667</v>
+      </c>
+      <c r="O88">
+        <v>-8.170893333333334</v>
+      </c>
+      <c r="P88">
+        <v>-32.68357333333334</v>
+      </c>
+      <c r="Q88">
+        <v>-28.95357333333333</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4071904795596218</v>
+      </c>
+      <c r="T88">
+        <v>6.541775156514617</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.02317069123971855</v>
+      </c>
+      <c r="W88">
+        <v>0.2332668389319552</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.1158534561985927</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2596161486198285</v>
+      </c>
+      <c r="C89">
+        <v>-142.2297072770688</v>
+      </c>
+      <c r="D89">
+        <v>52.87229272293116</v>
+      </c>
+      <c r="E89">
+        <v>143.05</v>
+      </c>
+      <c r="F89">
+        <v>195.75</v>
+      </c>
+      <c r="G89">
+        <v>0.648</v>
+      </c>
+      <c r="H89">
+        <v>172.3</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K89">
+        <v>3.73</v>
+      </c>
+      <c r="L89">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M89">
+        <v>46.7451</v>
+      </c>
+      <c r="N89">
+        <v>-41.39176666666667</v>
+      </c>
+      <c r="O89">
+        <v>-8.278353333333333</v>
+      </c>
+      <c r="P89">
+        <v>-33.11341333333333</v>
+      </c>
+      <c r="Q89">
+        <v>-29.38341333333333</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.4355282087565158</v>
+      </c>
+      <c r="T89">
+        <v>7.044988630092664</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.02290436145535397</v>
+      </c>
+      <c r="W89">
+        <v>0.2333304384844615</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.1145218072767697</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2616161486198285</v>
+      </c>
+      <c r="C90">
+        <v>-144.9542895104521</v>
+      </c>
+      <c r="D90">
+        <v>52.39771048954788</v>
+      </c>
+      <c r="E90">
+        <v>145.3</v>
+      </c>
+      <c r="F90">
+        <v>198</v>
+      </c>
+      <c r="G90">
+        <v>0.648</v>
+      </c>
+      <c r="H90">
+        <v>172.3</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K90">
+        <v>3.73</v>
+      </c>
+      <c r="L90">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M90">
+        <v>47.2824</v>
+      </c>
+      <c r="N90">
+        <v>-41.92906666666667</v>
+      </c>
+      <c r="O90">
+        <v>-8.385813333333335</v>
+      </c>
+      <c r="P90">
+        <v>-33.54325333333334</v>
+      </c>
+      <c r="Q90">
+        <v>-29.81325333333334</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.4685888928195588</v>
+      </c>
+      <c r="T90">
+        <v>7.632071015933721</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.02264408462063404</v>
+      </c>
+      <c r="W90">
+        <v>0.2333925925925926</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.1132204231031702</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2636161486198285</v>
+      </c>
+      <c r="C91">
+        <v>-147.6704278266827</v>
+      </c>
+      <c r="D91">
+        <v>51.93157217331729</v>
+      </c>
+      <c r="E91">
+        <v>147.55</v>
+      </c>
+      <c r="F91">
+        <v>200.25</v>
+      </c>
+      <c r="G91">
+        <v>0.648</v>
+      </c>
+      <c r="H91">
+        <v>172.3</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K91">
+        <v>3.73</v>
+      </c>
+      <c r="L91">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M91">
+        <v>47.8197</v>
+      </c>
+      <c r="N91">
+        <v>-42.46636666666667</v>
+      </c>
+      <c r="O91">
+        <v>-8.493273333333335</v>
+      </c>
+      <c r="P91">
+        <v>-33.97309333333334</v>
+      </c>
+      <c r="Q91">
+        <v>-30.24309333333334</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.5076606103486097</v>
+      </c>
+      <c r="T91">
+        <v>8.325895653745878</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.02238965670354826</v>
+      </c>
+      <c r="W91">
+        <v>0.2334533499791927</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.1119482835177412</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2656161486198286</v>
+      </c>
+      <c r="C92">
+        <v>-150.378345593908</v>
+      </c>
+      <c r="D92">
+        <v>51.47365440609197</v>
+      </c>
+      <c r="E92">
+        <v>149.8</v>
+      </c>
+      <c r="F92">
+        <v>202.5</v>
+      </c>
+      <c r="G92">
+        <v>0.648</v>
+      </c>
+      <c r="H92">
+        <v>172.3</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K92">
+        <v>3.73</v>
+      </c>
+      <c r="L92">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M92">
+        <v>48.357</v>
+      </c>
+      <c r="N92">
+        <v>-43.00366666666667</v>
+      </c>
+      <c r="O92">
+        <v>-8.600733333333334</v>
+      </c>
+      <c r="P92">
+        <v>-34.40293333333334</v>
+      </c>
+      <c r="Q92">
+        <v>-30.67293333333334</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.5545466713834706</v>
+      </c>
+      <c r="T92">
+        <v>9.158485219120466</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.0221408827401755</v>
+      </c>
+      <c r="W92">
+        <v>0.2335127572016461</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.1107044137008775</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2676161486198286</v>
+      </c>
+      <c r="C93">
+        <v>-153.0782583707515</v>
+      </c>
+      <c r="D93">
+        <v>51.02374162924845</v>
+      </c>
+      <c r="E93">
+        <v>152.05</v>
+      </c>
+      <c r="F93">
+        <v>204.75</v>
+      </c>
+      <c r="G93">
+        <v>0.648</v>
+      </c>
+      <c r="H93">
+        <v>172.3</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K93">
+        <v>3.73</v>
+      </c>
+      <c r="L93">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M93">
+        <v>48.8943</v>
+      </c>
+      <c r="N93">
+        <v>-43.54096666666667</v>
+      </c>
+      <c r="O93">
+        <v>-8.708193333333334</v>
+      </c>
+      <c r="P93">
+        <v>-34.83277333333334</v>
+      </c>
+      <c r="Q93">
+        <v>-31.10277333333334</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.6118518570927454</v>
+      </c>
+      <c r="T93">
+        <v>10.17609468791163</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.02189757633643731</v>
+      </c>
+      <c r="W93">
+        <v>0.2335708587708588</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.1094878816821865</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2696161486198285</v>
+      </c>
+      <c r="C94">
+        <v>-155.7703742446568</v>
+      </c>
+      <c r="D94">
+        <v>50.58162575534322</v>
+      </c>
+      <c r="E94">
+        <v>154.3</v>
+      </c>
+      <c r="F94">
+        <v>207</v>
+      </c>
+      <c r="G94">
+        <v>0.648</v>
+      </c>
+      <c r="H94">
+        <v>172.3</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K94">
+        <v>3.73</v>
+      </c>
+      <c r="L94">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M94">
+        <v>49.4316</v>
+      </c>
+      <c r="N94">
+        <v>-44.07826666666667</v>
+      </c>
+      <c r="O94">
+        <v>-8.815653333333335</v>
+      </c>
+      <c r="P94">
+        <v>-35.26261333333333</v>
+      </c>
+      <c r="Q94">
+        <v>-31.53261333333333</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.6834833392293387</v>
+      </c>
+      <c r="T94">
+        <v>11.44810652390059</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.0216595592023456</v>
+      </c>
+      <c r="W94">
+        <v>0.2336276972624799</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.108297796011728</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2716161486198286</v>
+      </c>
+      <c r="C95">
+        <v>-158.454894152792</v>
+      </c>
+      <c r="D95">
+        <v>50.14710584720798</v>
+      </c>
+      <c r="E95">
+        <v>156.55</v>
+      </c>
+      <c r="F95">
+        <v>209.25</v>
+      </c>
+      <c r="G95">
+        <v>0.648</v>
+      </c>
+      <c r="H95">
+        <v>172.3</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K95">
+        <v>3.73</v>
+      </c>
+      <c r="L95">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M95">
+        <v>49.9689</v>
+      </c>
+      <c r="N95">
+        <v>-44.61556666666667</v>
+      </c>
+      <c r="O95">
+        <v>-8.923113333333335</v>
+      </c>
+      <c r="P95">
+        <v>-35.69245333333334</v>
+      </c>
+      <c r="Q95">
+        <v>-31.96245333333334</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.7755809591192442</v>
+      </c>
+      <c r="T95">
+        <v>13.08355031302924</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.02142666071629887</v>
+      </c>
+      <c r="W95">
+        <v>0.2336833134209478</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.1071333035814943</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2736161486198286</v>
+      </c>
+      <c r="C96">
+        <v>-161.1320121865555</v>
+      </c>
+      <c r="D96">
+        <v>49.71998781344449</v>
+      </c>
+      <c r="E96">
+        <v>158.8</v>
+      </c>
+      <c r="F96">
+        <v>211.5</v>
+      </c>
+      <c r="G96">
+        <v>0.648</v>
+      </c>
+      <c r="H96">
+        <v>172.3</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K96">
+        <v>3.73</v>
+      </c>
+      <c r="L96">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M96">
+        <v>50.5062</v>
+      </c>
+      <c r="N96">
+        <v>-45.15286666666667</v>
+      </c>
+      <c r="O96">
+        <v>-9.030573333333335</v>
+      </c>
+      <c r="P96">
+        <v>-36.12229333333333</v>
+      </c>
+      <c r="Q96">
+        <v>-32.39229333333333</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.8983777856391184</v>
+      </c>
+      <c r="T96">
+        <v>15.26414203186746</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.02119871751718931</v>
+      </c>
+      <c r="W96">
+        <v>0.2337377462568952</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.1059935875859465</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2756161486198286</v>
+      </c>
+      <c r="C97">
+        <v>-163.8019158806508</v>
+      </c>
+      <c r="D97">
+        <v>49.30008411934919</v>
+      </c>
+      <c r="E97">
+        <v>161.05</v>
+      </c>
+      <c r="F97">
+        <v>213.75</v>
+      </c>
+      <c r="G97">
+        <v>0.648</v>
+      </c>
+      <c r="H97">
+        <v>172.3</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K97">
+        <v>3.73</v>
+      </c>
+      <c r="L97">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M97">
+        <v>51.04350000000001</v>
+      </c>
+      <c r="N97">
+        <v>-45.69016666666668</v>
+      </c>
+      <c r="O97">
+        <v>-9.138033333333336</v>
+      </c>
+      <c r="P97">
+        <v>-36.55213333333334</v>
+      </c>
+      <c r="Q97">
+        <v>-32.82213333333334</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.070293342766943</v>
+      </c>
+      <c r="T97">
+        <v>18.31697043824095</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.02097557312227152</v>
+      </c>
+      <c r="W97">
+        <v>0.2337910331384016</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.1048778656113576</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2776161486198285</v>
+      </c>
+      <c r="C98">
+        <v>-166.4647864876367</v>
+      </c>
+      <c r="D98">
+        <v>48.88721351236332</v>
+      </c>
+      <c r="E98">
+        <v>163.3</v>
+      </c>
+      <c r="F98">
+        <v>216</v>
+      </c>
+      <c r="G98">
+        <v>0.648</v>
+      </c>
+      <c r="H98">
+        <v>172.3</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K98">
+        <v>3.73</v>
+      </c>
+      <c r="L98">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M98">
+        <v>51.5808</v>
+      </c>
+      <c r="N98">
+        <v>-46.22746666666667</v>
+      </c>
+      <c r="O98">
+        <v>-9.245493333333334</v>
+      </c>
+      <c r="P98">
+        <v>-36.98197333333334</v>
+      </c>
+      <c r="Q98">
+        <v>-33.25197333333334</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.328166678458675</v>
+      </c>
+      <c r="T98">
+        <v>22.89621304780114</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.02075707756891453</v>
+      </c>
+      <c r="W98">
+        <v>0.2338432098765432</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.1037853878445726</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2796161486198285</v>
+      </c>
+      <c r="C99">
+        <v>-169.120799238796</v>
+      </c>
+      <c r="D99">
+        <v>48.48120076120401</v>
+      </c>
+      <c r="E99">
+        <v>165.55</v>
+      </c>
+      <c r="F99">
+        <v>218.25</v>
+      </c>
+      <c r="G99">
+        <v>0.648</v>
+      </c>
+      <c r="H99">
+        <v>172.3</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K99">
+        <v>3.73</v>
+      </c>
+      <c r="L99">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M99">
+        <v>52.11810000000001</v>
+      </c>
+      <c r="N99">
+        <v>-46.76476666666667</v>
+      </c>
+      <c r="O99">
+        <v>-9.352953333333335</v>
+      </c>
+      <c r="P99">
+        <v>-37.41181333333334</v>
+      </c>
+      <c r="Q99">
+        <v>-33.68181333333334</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.757955571278234</v>
+      </c>
+      <c r="T99">
+        <v>30.52828406373486</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.02054308707851335</v>
+      </c>
+      <c r="W99">
+        <v>0.233894310805651</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.1027154353925667</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2816161486198285</v>
+      </c>
+      <c r="C100">
+        <v>-171.7701235921124</v>
+      </c>
+      <c r="D100">
+        <v>48.08187640788754</v>
+      </c>
+      <c r="E100">
+        <v>167.8</v>
+      </c>
+      <c r="F100">
+        <v>220.5</v>
+      </c>
+      <c r="G100">
+        <v>0.648</v>
+      </c>
+      <c r="H100">
+        <v>172.3</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K100">
+        <v>3.73</v>
+      </c>
+      <c r="L100">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M100">
+        <v>52.6554</v>
+      </c>
+      <c r="N100">
+        <v>-47.30206666666667</v>
+      </c>
+      <c r="O100">
+        <v>-9.460413333333333</v>
+      </c>
+      <c r="P100">
+        <v>-37.84165333333333</v>
+      </c>
+      <c r="Q100">
+        <v>-34.11165333333334</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.617533356917351</v>
+      </c>
+      <c r="T100">
+        <v>45.79242609560228</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.0203334637409775</v>
+      </c>
+      <c r="W100">
+        <v>0.2339443688586546</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.1016673187048874</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2836161486198285</v>
+      </c>
+      <c r="C101">
+        <v>-174.4129234680925</v>
+      </c>
+      <c r="D101">
+        <v>47.68907653190752</v>
+      </c>
+      <c r="E101">
+        <v>170.05</v>
+      </c>
+      <c r="F101">
+        <v>222.75</v>
+      </c>
+      <c r="G101">
+        <v>0.648</v>
+      </c>
+      <c r="H101">
+        <v>172.3</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>9.083333333333334</v>
+      </c>
+      <c r="K101">
+        <v>3.73</v>
+      </c>
+      <c r="L101">
+        <v>5.353333333333333</v>
+      </c>
+      <c r="M101">
+        <v>53.1927</v>
+      </c>
+      <c r="N101">
+        <v>-47.83936666666667</v>
+      </c>
+      <c r="O101">
+        <v>-9.567873333333335</v>
+      </c>
+      <c r="P101">
+        <v>-38.27149333333334</v>
+      </c>
+      <c r="Q101">
+        <v>-34.54149333333334</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>5.196266713834701</v>
+      </c>
+      <c r="T101">
+        <v>91.58485219120456</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.02012807521834136</v>
+      </c>
+      <c r="W101">
+        <v>0.2339934156378601</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.1006403760917068</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
